--- a/Design-Files/OFP_VIM_v1.5/BOM/eSpark-BOM-OFP_VIM_v1.5.xlsx
+++ b/Design-Files/OFP_VIM_v1.5/BOM/eSpark-BOM-OFP_VIM_v1.5.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="10 Boards" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="382">
   <si>
     <t>Component list</t>
   </si>
@@ -175,9 +175,6 @@
     <t>L1, L2, L3, L5, L6, L7</t>
   </si>
   <si>
-    <t>L4</t>
-  </si>
-  <si>
     <t>Q1</t>
   </si>
   <si>
@@ -310,12 +307,6 @@
     <t>CONN HDR 24POS 0.1 GOLD PCB R/A</t>
   </si>
   <si>
-    <t>450V 17.5A 4 Bend -40℃~+105℃ 1 5.08mm Green Board Edge/Receptacle-Open Push-Pull,P=5.08mm Pluggable System Terminal Block ROHS</t>
-  </si>
-  <si>
-    <t>450V 17.5A 4 -40℃~+105℃ 1.5 1 14~28 5.08mm 1x4P Green Plug P=5.08mm Pluggable System Terminal Block ROHS</t>
-  </si>
-  <si>
     <t>420mA 470uH EI-core Inductor ±20% Plugin Power Inductors ROHS</t>
   </si>
   <si>
@@ -427,9 +418,6 @@
     <t>SFH11-PBPC-D12-RA-BK</t>
   </si>
   <si>
-    <t>DB2ER-5.08-4P-GN</t>
-  </si>
-  <si>
     <t>PK0810-471MB</t>
   </si>
   <si>
@@ -517,9 +505,6 @@
     <t>BLM21BD152SN1D</t>
   </si>
   <si>
-    <t>DB2EK-5.08-4P-GN-S</t>
-  </si>
-  <si>
     <t>IPD90R1K2C3</t>
   </si>
   <si>
@@ -616,12 +601,6 @@
     <t>Sullins</t>
   </si>
   <si>
-    <t>DIBO</t>
-  </si>
-  <si>
-    <t>DORABO</t>
-  </si>
-  <si>
     <t>SXN(Shun Xiang Nuo Elec)</t>
   </si>
   <si>
@@ -700,12 +679,6 @@
     <t>C108518</t>
   </si>
   <si>
-    <t>C395752</t>
-  </si>
-  <si>
-    <t>C395757</t>
-  </si>
-  <si>
     <t>C400319</t>
   </si>
   <si>
@@ -964,12 +937,6 @@
     <t>LCSC</t>
   </si>
   <si>
-    <t>0.1510</t>
-  </si>
-  <si>
-    <t>0.3389</t>
-  </si>
-  <si>
     <t>0.0861</t>
   </si>
   <si>
@@ -1117,12 +1084,6 @@
     <t>0.1865</t>
   </si>
   <si>
-    <t>0.0909</t>
-  </si>
-  <si>
-    <t>0.2219</t>
-  </si>
-  <si>
     <t>0.0544</t>
   </si>
   <si>
@@ -1175,6 +1136,36 @@
   </si>
   <si>
     <t>0.1318</t>
+  </si>
+  <si>
+    <t>T1</t>
+  </si>
+  <si>
+    <t>12V/1.5A transformer</t>
+  </si>
+  <si>
+    <t>FTEFD25-037</t>
+  </si>
+  <si>
+    <t>Plugin,P=3.81mm Pluggable System Terminal Block ROHS</t>
+  </si>
+  <si>
+    <t>KF2EDGRG-3.81-4P</t>
+  </si>
+  <si>
+    <t>Cixi Kefa Elec</t>
+  </si>
+  <si>
+    <t>-40℃~+105℃ 1.5 1 16~28 3.81mm 160V 7A 4 1x4P Green Plug Snap Fit P=3.81mm Pluggable System Terminal Block ROHS</t>
+  </si>
+  <si>
+    <t>KF2EDGKNG-3.81-4P</t>
+  </si>
+  <si>
+    <t>C6392932</t>
+  </si>
+  <si>
+    <t>C2923028</t>
   </si>
 </sst>
 </file>
@@ -1640,17 +1631,6 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1668,6 +1648,17 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1990,14 +1981,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48"/>
+      <c r="R1" s="48"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1">
       <c r="A2" s="1"/>
@@ -2008,7 +1999,7 @@
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="40" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="3"/>
@@ -2032,7 +2023,7 @@
       </c>
       <c r="E3" s="27"/>
       <c r="F3" s="41" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="G3" s="29"/>
       <c r="H3" s="30"/>
@@ -2119,46 +2110,46 @@
         <v>25</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="L7" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="M7" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="N7" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="O7" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="P7" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q7" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="M7" s="12" t="s">
-        <v>283</v>
-      </c>
-      <c r="N7" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="O7" s="12" t="s">
-        <v>285</v>
-      </c>
-      <c r="P7" s="12" t="s">
-        <v>286</v>
-      </c>
-      <c r="Q7" s="12" t="s">
-        <v>287</v>
-      </c>
       <c r="R7" s="12" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="24">
@@ -2174,25 +2165,25 @@
         <v>26</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="K8" s="45" t="s">
-        <v>289</v>
+        <v>199</v>
+      </c>
+      <c r="K8" s="42" t="s">
+        <v>280</v>
       </c>
       <c r="L8" s="14">
         <v>2</v>
@@ -2204,11 +2195,11 @@
       <c r="N8" s="14">
         <v>25</v>
       </c>
-      <c r="O8" s="47" t="s">
-        <v>313</v>
+      <c r="O8" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P8" s="15" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="Q8" s="15">
         <f>P8*N8</f>
@@ -2229,25 +2220,25 @@
         <v>27</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J9" s="20" t="s">
-        <v>207</v>
-      </c>
-      <c r="K9" s="46" t="s">
-        <v>249</v>
+        <v>200</v>
+      </c>
+      <c r="K9" s="43" t="s">
+        <v>240</v>
       </c>
       <c r="L9" s="20">
         <v>3</v>
@@ -2259,8 +2250,8 @@
       <c r="N9" s="20">
         <v>35</v>
       </c>
-      <c r="O9" s="47" t="s">
-        <v>313</v>
+      <c r="O9" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P9" s="21">
         <v>0.21310000000000001</v>
@@ -2284,25 +2275,25 @@
         <v>28</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="K10" s="45" t="s">
-        <v>250</v>
+        <v>201</v>
+      </c>
+      <c r="K10" s="42" t="s">
+        <v>241</v>
       </c>
       <c r="L10" s="14">
         <v>2</v>
@@ -2314,11 +2305,11 @@
       <c r="N10" s="14">
         <v>21</v>
       </c>
-      <c r="O10" s="47" t="s">
-        <v>313</v>
+      <c r="O10" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P10" s="15" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="Q10" s="15">
         <f>P10*N10</f>
@@ -2339,25 +2330,25 @@
         <v>29</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J11" s="20" t="s">
-        <v>209</v>
-      </c>
-      <c r="K11" s="46" t="s">
-        <v>251</v>
+        <v>202</v>
+      </c>
+      <c r="K11" s="43" t="s">
+        <v>242</v>
       </c>
       <c r="L11" s="20">
         <v>4</v>
@@ -2369,11 +2360,11 @@
       <c r="N11" s="20">
         <v>45</v>
       </c>
-      <c r="O11" s="47" t="s">
-        <v>313</v>
+      <c r="O11" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P11" s="21" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="Q11" s="21">
         <f t="shared" ref="Q11" si="3">P11*N11</f>
@@ -2394,25 +2385,25 @@
         <v>30</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>210</v>
-      </c>
-      <c r="K12" s="45" t="s">
-        <v>252</v>
+        <v>203</v>
+      </c>
+      <c r="K12" s="42" t="s">
+        <v>243</v>
       </c>
       <c r="L12" s="14">
         <v>1</v>
@@ -2422,13 +2413,13 @@
         <v>10</v>
       </c>
       <c r="N12" s="14" t="s">
-        <v>310</v>
-      </c>
-      <c r="O12" s="47" t="s">
-        <v>313</v>
+        <v>301</v>
+      </c>
+      <c r="O12" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P12" s="15" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="Q12" s="15">
         <f>P12*N12</f>
@@ -2449,25 +2440,25 @@
         <v>31</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J13" s="20" t="s">
-        <v>211</v>
-      </c>
-      <c r="K13" s="46" t="s">
-        <v>253</v>
+        <v>204</v>
+      </c>
+      <c r="K13" s="43" t="s">
+        <v>244</v>
       </c>
       <c r="L13" s="20">
         <v>1</v>
@@ -2479,11 +2470,11 @@
       <c r="N13" s="20">
         <v>15</v>
       </c>
-      <c r="O13" s="47" t="s">
-        <v>313</v>
+      <c r="O13" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P13" s="21" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="Q13" s="21">
         <f t="shared" ref="Q13" si="4">P13*N13</f>
@@ -2504,25 +2495,25 @@
         <v>32</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="K14" s="45" t="s">
-        <v>252</v>
+        <v>205</v>
+      </c>
+      <c r="K14" s="42" t="s">
+        <v>243</v>
       </c>
       <c r="L14" s="14">
         <v>1</v>
@@ -2534,11 +2525,11 @@
       <c r="N14" s="14">
         <v>15</v>
       </c>
-      <c r="O14" s="47" t="s">
-        <v>313</v>
+      <c r="O14" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P14" s="15" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="Q14" s="15">
         <f>P14*N14</f>
@@ -2559,25 +2550,25 @@
         <v>33</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J15" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="K15" s="46" t="s">
-        <v>254</v>
+        <v>206</v>
+      </c>
+      <c r="K15" s="43" t="s">
+        <v>245</v>
       </c>
       <c r="L15" s="20">
         <v>1</v>
@@ -2589,11 +2580,11 @@
       <c r="N15" s="20">
         <v>15</v>
       </c>
-      <c r="O15" s="47" t="s">
-        <v>313</v>
+      <c r="O15" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P15" s="21" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="Q15" s="21">
         <f t="shared" ref="Q15" si="5">P15*N15</f>
@@ -2614,25 +2605,25 @@
         <v>34</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="K16" s="45" t="s">
-        <v>255</v>
+        <v>207</v>
+      </c>
+      <c r="K16" s="42" t="s">
+        <v>246</v>
       </c>
       <c r="L16" s="14">
         <v>1</v>
@@ -2642,13 +2633,13 @@
         <v>10</v>
       </c>
       <c r="N16" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="O16" s="47" t="s">
-        <v>313</v>
+        <v>302</v>
+      </c>
+      <c r="O16" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P16" s="15" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="Q16" s="15">
         <f>P16*N16</f>
@@ -2669,25 +2660,25 @@
         <v>35</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J17" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="K17" s="46" t="s">
-        <v>256</v>
+        <v>208</v>
+      </c>
+      <c r="K17" s="43" t="s">
+        <v>247</v>
       </c>
       <c r="L17" s="20">
         <v>2</v>
@@ -2699,11 +2690,11 @@
       <c r="N17" s="20">
         <v>40</v>
       </c>
-      <c r="O17" s="47" t="s">
-        <v>313</v>
+      <c r="O17" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P17" s="21" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="Q17" s="21">
         <f t="shared" ref="Q17" si="6">P17*N17</f>
@@ -2724,25 +2715,25 @@
         <v>36</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>216</v>
-      </c>
-      <c r="K18" s="45" t="s">
-        <v>257</v>
+        <v>209</v>
+      </c>
+      <c r="K18" s="42" t="s">
+        <v>248</v>
       </c>
       <c r="L18" s="14">
         <v>1</v>
@@ -2752,13 +2743,13 @@
         <v>10</v>
       </c>
       <c r="N18" s="14" t="s">
-        <v>312</v>
-      </c>
-      <c r="O18" s="47" t="s">
-        <v>313</v>
+        <v>303</v>
+      </c>
+      <c r="O18" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P18" s="15" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="Q18" s="15">
         <f>P18*N18</f>
@@ -2779,25 +2770,25 @@
         <v>37</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J19" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="K19" s="46" t="s">
-        <v>258</v>
+        <v>210</v>
+      </c>
+      <c r="K19" s="43" t="s">
+        <v>249</v>
       </c>
       <c r="L19" s="20">
         <v>1</v>
@@ -2807,13 +2798,13 @@
         <v>10</v>
       </c>
       <c r="N19" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="O19" s="47" t="s">
-        <v>313</v>
+        <v>302</v>
+      </c>
+      <c r="O19" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P19" s="21" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" ref="Q19" si="7">P19*N19</f>
@@ -2834,25 +2825,25 @@
         <v>38</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>218</v>
-      </c>
-      <c r="K20" s="45" t="s">
-        <v>259</v>
+        <v>211</v>
+      </c>
+      <c r="K20" s="42" t="s">
+        <v>250</v>
       </c>
       <c r="L20" s="14">
         <v>3</v>
@@ -2864,11 +2855,11 @@
       <c r="N20" s="14">
         <v>32</v>
       </c>
-      <c r="O20" s="47" t="s">
-        <v>313</v>
+      <c r="O20" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P20" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="Q20" s="15">
         <f>P20*N20</f>
@@ -2889,25 +2880,25 @@
         <v>39</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G21" s="20" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J21" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="K21" s="46" t="s">
-        <v>260</v>
+        <v>280</v>
+      </c>
+      <c r="K21" s="43" t="s">
+        <v>251</v>
       </c>
       <c r="L21" s="20">
         <v>6</v>
@@ -2919,8 +2910,8 @@
       <c r="N21" s="20">
         <v>61</v>
       </c>
-      <c r="O21" s="47" t="s">
-        <v>337</v>
+      <c r="O21" s="44" t="s">
+        <v>326</v>
       </c>
       <c r="P21" s="21">
         <v>2.1000000000000001E-2</v>
@@ -2944,25 +2935,25 @@
         <v>40</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>219</v>
-      </c>
-      <c r="K22" s="45" t="s">
-        <v>289</v>
+        <v>212</v>
+      </c>
+      <c r="K22" s="42" t="s">
+        <v>280</v>
       </c>
       <c r="L22" s="14">
         <v>1</v>
@@ -2974,11 +2965,11 @@
       <c r="N22" s="14">
         <v>11</v>
       </c>
-      <c r="O22" s="47" t="s">
-        <v>313</v>
+      <c r="O22" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P22" s="15" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="Q22" s="15">
         <f>P22*N22</f>
@@ -2999,25 +2990,25 @@
         <v>41</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="H23" s="20" t="s">
         <v>11</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J23" s="20" t="s">
-        <v>220</v>
-      </c>
-      <c r="K23" s="46" t="s">
-        <v>261</v>
+        <v>213</v>
+      </c>
+      <c r="K23" s="43" t="s">
+        <v>252</v>
       </c>
       <c r="L23" s="20">
         <v>1</v>
@@ -3027,13 +3018,13 @@
         <v>10</v>
       </c>
       <c r="N23" s="20" t="s">
-        <v>310</v>
-      </c>
-      <c r="O23" s="47" t="s">
-        <v>313</v>
+        <v>301</v>
+      </c>
+      <c r="O23" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P23" s="21" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="Q23" s="21">
         <f t="shared" ref="Q23" si="9">P23*N23</f>
@@ -3054,25 +3045,25 @@
         <v>42</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="H24" s="14" t="s">
         <v>11</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>221</v>
-      </c>
-      <c r="K24" s="45" t="s">
-        <v>289</v>
+        <v>214</v>
+      </c>
+      <c r="K24" s="42" t="s">
+        <v>280</v>
       </c>
       <c r="L24" s="14">
         <v>1</v>
@@ -3084,11 +3075,11 @@
       <c r="N24" s="14">
         <v>20</v>
       </c>
-      <c r="O24" s="47" t="s">
-        <v>313</v>
+      <c r="O24" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P24" s="15" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="Q24" s="15">
         <f>P24*N24</f>
@@ -3109,25 +3100,25 @@
         <v>43</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="H25" s="20" t="s">
         <v>11</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J25" s="20" t="s">
-        <v>222</v>
-      </c>
-      <c r="K25" s="45" t="s">
-        <v>289</v>
+        <v>215</v>
+      </c>
+      <c r="K25" s="42" t="s">
+        <v>280</v>
       </c>
       <c r="L25" s="20">
         <v>1</v>
@@ -3139,11 +3130,11 @@
       <c r="N25" s="20">
         <v>15</v>
       </c>
-      <c r="O25" s="47" t="s">
-        <v>313</v>
+      <c r="O25" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P25" s="21" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="Q25" s="21">
         <f t="shared" ref="Q25" si="10">P25*N25</f>
@@ -3164,25 +3155,25 @@
         <v>44</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F26" s="20" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="K26" s="45" t="s">
-        <v>289</v>
+        <v>216</v>
+      </c>
+      <c r="K26" s="42" t="s">
+        <v>280</v>
       </c>
       <c r="L26" s="14">
         <v>1</v>
@@ -3194,11 +3185,11 @@
       <c r="N26" s="14">
         <v>15</v>
       </c>
-      <c r="O26" s="47" t="s">
-        <v>313</v>
+      <c r="O26" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P26" s="15" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="Q26" s="15">
         <f>P26*N26</f>
@@ -3219,25 +3210,25 @@
         <v>45</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J27" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="K27" s="45" t="s">
-        <v>289</v>
+        <v>217</v>
+      </c>
+      <c r="K27" s="42" t="s">
+        <v>280</v>
       </c>
       <c r="L27" s="20">
         <v>4</v>
@@ -3249,11 +3240,11 @@
       <c r="N27" s="20">
         <v>50</v>
       </c>
-      <c r="O27" s="47" t="s">
-        <v>313</v>
+      <c r="O27" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P27" s="21" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="Q27" s="21">
         <f t="shared" ref="Q27" si="11">P27*N27</f>
@@ -3274,25 +3265,25 @@
         <v>46</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F28" s="20" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="K28" s="45" t="s">
-        <v>289</v>
+        <v>218</v>
+      </c>
+      <c r="K28" s="42" t="s">
+        <v>280</v>
       </c>
       <c r="L28" s="14">
         <v>1</v>
@@ -3304,11 +3295,11 @@
       <c r="N28" s="14">
         <v>11</v>
       </c>
-      <c r="O28" s="47" t="s">
-        <v>313</v>
+      <c r="O28" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P28" s="15" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="Q28" s="15">
         <f>P28*N28</f>
@@ -3329,25 +3320,25 @@
         <v>47</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="G29" s="20" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I29" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J29" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="K29" s="45" t="s">
-        <v>289</v>
+        <v>280</v>
+      </c>
+      <c r="K29" s="42" t="s">
+        <v>280</v>
       </c>
       <c r="L29" s="20">
         <v>1</v>
@@ -3359,8 +3350,8 @@
       <c r="N29" s="20">
         <v>11</v>
       </c>
-      <c r="O29" s="47" t="s">
-        <v>337</v>
+      <c r="O29" s="44" t="s">
+        <v>326</v>
       </c>
       <c r="P29" s="21">
         <v>1.8387</v>
@@ -3371,7 +3362,7 @@
       </c>
       <c r="R29" s="20"/>
     </row>
-    <row r="30" spans="1:18" ht="60">
+    <row r="30" spans="1:18" ht="24">
       <c r="A30" s="1"/>
       <c r="B30" s="16">
         <f>ROW(B30) - ROW($B$7)</f>
@@ -3383,26 +3374,26 @@
       <c r="D30" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E30" s="14" t="s">
-        <v>96</v>
+      <c r="E30" s="42" t="s">
+        <v>375</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>290</v>
-      </c>
-      <c r="G30" s="14" t="s">
-        <v>135</v>
+        <v>281</v>
+      </c>
+      <c r="G30" s="42" t="s">
+        <v>376</v>
       </c>
       <c r="H30" s="14" t="s">
-        <v>198</v>
+        <v>377</v>
       </c>
       <c r="I30" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>226</v>
-      </c>
-      <c r="K30" s="45" t="s">
-        <v>289</v>
+        <v>380</v>
+      </c>
+      <c r="K30" s="42" t="s">
+        <v>280</v>
       </c>
       <c r="L30" s="14">
         <v>1</v>
@@ -3414,15 +3405,15 @@
       <c r="N30" s="14">
         <v>15</v>
       </c>
-      <c r="O30" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P30" s="15" t="s">
-        <v>314</v>
+      <c r="O30" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P30" s="15">
+        <v>0.18529999999999999</v>
       </c>
       <c r="Q30" s="15">
         <f>P30*N30</f>
-        <v>2.2650000000000001</v>
+        <v>2.7795000000000001</v>
       </c>
       <c r="R30" s="14"/>
     </row>
@@ -3438,26 +3429,26 @@
       <c r="D31" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="E31" s="20" t="s">
-        <v>97</v>
+      <c r="E31" s="43" t="s">
+        <v>378</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>290</v>
-      </c>
-      <c r="G31" s="20" t="s">
-        <v>165</v>
+        <v>281</v>
+      </c>
+      <c r="G31" s="43" t="s">
+        <v>379</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>199</v>
+        <v>377</v>
       </c>
       <c r="I31" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J31" s="20" t="s">
-        <v>227</v>
-      </c>
-      <c r="K31" s="45" t="s">
-        <v>289</v>
+        <v>381</v>
+      </c>
+      <c r="K31" s="42" t="s">
+        <v>280</v>
       </c>
       <c r="L31" s="20">
         <v>1</v>
@@ -3469,15 +3460,15 @@
       <c r="N31" s="20">
         <v>11</v>
       </c>
-      <c r="O31" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P31" s="21" t="s">
-        <v>315</v>
+      <c r="O31" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P31" s="21">
+        <v>0.50419999999999998</v>
       </c>
       <c r="Q31" s="21">
         <f t="shared" ref="Q31" si="13">P31*N31</f>
-        <v>3.7279</v>
+        <v>5.5461999999999998</v>
       </c>
       <c r="R31" s="20"/>
     </row>
@@ -3494,25 +3485,25 @@
         <v>50</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H32" s="14" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="I32" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>228</v>
-      </c>
-      <c r="K32" s="45" t="s">
-        <v>262</v>
+        <v>219</v>
+      </c>
+      <c r="K32" s="42" t="s">
+        <v>253</v>
       </c>
       <c r="L32" s="14">
         <v>6</v>
@@ -3524,11 +3515,11 @@
       <c r="N32" s="14">
         <v>65</v>
       </c>
-      <c r="O32" s="47" t="s">
-        <v>313</v>
+      <c r="O32" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P32" s="15" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="Q32" s="15">
         <f>P32*N32</f>
@@ -3536,1048 +3527,1048 @@
       </c>
       <c r="R32" s="14"/>
     </row>
-    <row r="33" spans="1:18">
+    <row r="33" spans="1:18" ht="24">
       <c r="A33" s="1"/>
-      <c r="B33" s="17">
+      <c r="B33" s="16">
+        <f>ROW(B33) - ROW($B$7)</f>
+        <v>26</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="H33" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="I33" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="J33" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="K33" s="43" t="s">
+        <v>280</v>
+      </c>
+      <c r="L33" s="14">
+        <v>1</v>
+      </c>
+      <c r="M33" s="14">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N33" s="14">
+        <v>11</v>
+      </c>
+      <c r="O33" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P33" s="15" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q33" s="15">
+        <f>P33*N33</f>
+        <v>7.8759999999999994</v>
+      </c>
+      <c r="R33" s="14"/>
+    </row>
+    <row r="34" spans="1:18" ht="25.5">
+      <c r="A34" s="1"/>
+      <c r="B34" s="17">
         <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="C33" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="D33" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="E33" s="46" t="s">
-        <v>289</v>
-      </c>
-      <c r="F33" s="20" t="s">
-        <v>290</v>
-      </c>
-      <c r="G33" s="46" t="s">
-        <v>289</v>
-      </c>
-      <c r="H33" s="20"/>
-      <c r="I33" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="J33" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="K33" s="46" t="s">
-        <v>289</v>
-      </c>
-      <c r="L33" s="20">
-        <v>1</v>
-      </c>
-      <c r="M33" s="14">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="N33" s="20">
-        <v>11</v>
-      </c>
-      <c r="O33" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="P33" s="21">
+        <v>27</v>
+      </c>
+      <c r="C34" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="F34" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="G34" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="H34" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="I34" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="J34" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="K34" s="43" t="s">
+        <v>254</v>
+      </c>
+      <c r="L34" s="20">
         <v>3</v>
       </c>
-      <c r="Q33" s="21">
-        <f t="shared" ref="Q33" si="14">P33*N33</f>
-        <v>33</v>
-      </c>
-      <c r="R33" s="20"/>
-    </row>
-    <row r="34" spans="1:18" ht="24">
-      <c r="A34" s="1"/>
-      <c r="B34" s="16">
-        <f>ROW(B34) - ROW($B$7)</f>
-        <v>27</v>
-      </c>
-      <c r="C34" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="E34" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="F34" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="G34" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="H34" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="I34" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="J34" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="K34" s="46" t="s">
-        <v>289</v>
-      </c>
-      <c r="L34" s="14">
-        <v>1</v>
-      </c>
       <c r="M34" s="14">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="N34" s="14">
-        <v>11</v>
-      </c>
-      <c r="O34" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P34" s="15" t="s">
-        <v>317</v>
-      </c>
-      <c r="Q34" s="15">
-        <f>P34*N34</f>
-        <v>7.8759999999999994</v>
-      </c>
-      <c r="R34" s="14"/>
-    </row>
-    <row r="35" spans="1:18" ht="25.5">
+        <v>30</v>
+      </c>
+      <c r="N34" s="20">
+        <v>40</v>
+      </c>
+      <c r="O34" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P34" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q34" s="21">
+        <f t="shared" ref="Q34" si="14">P34*N34</f>
+        <v>2.6719999999999997</v>
+      </c>
+      <c r="R34" s="20"/>
+    </row>
+    <row r="35" spans="1:18">
       <c r="A35" s="1"/>
-      <c r="B35" s="17">
-        <f t="shared" si="0"/>
+      <c r="B35" s="16">
+        <f>ROW(B35) - ROW($B$7)</f>
         <v>28</v>
       </c>
-      <c r="C35" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="D35" s="20" t="s">
+      <c r="C35" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D35" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E35" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="F35" s="20" t="s">
-        <v>290</v>
-      </c>
-      <c r="G35" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="H35" s="20" t="s">
-        <v>194</v>
+      <c r="E35" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="H35" s="14" t="s">
+        <v>189</v>
       </c>
       <c r="I35" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="J35" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="K35" s="46" t="s">
-        <v>263</v>
-      </c>
-      <c r="L35" s="20">
-        <v>3</v>
+        <v>280</v>
+      </c>
+      <c r="J35" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="K35" s="42" t="s">
+        <v>255</v>
+      </c>
+      <c r="L35" s="14">
+        <v>6</v>
       </c>
       <c r="M35" s="14">
         <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="N35" s="20">
-        <v>40</v>
-      </c>
-      <c r="O35" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P35" s="21" t="s">
-        <v>318</v>
-      </c>
-      <c r="Q35" s="21">
-        <f t="shared" ref="Q35" si="15">P35*N35</f>
-        <v>2.6719999999999997</v>
-      </c>
-      <c r="R35" s="20"/>
+        <v>60</v>
+      </c>
+      <c r="N35" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="O35" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P35" s="15" t="s">
+        <v>308</v>
+      </c>
+      <c r="Q35" s="15">
+        <f>P35*N35</f>
+        <v>1.04</v>
+      </c>
+      <c r="R35" s="14"/>
     </row>
     <row r="36" spans="1:18">
       <c r="A36" s="1"/>
-      <c r="B36" s="16">
-        <f>ROW(B36) - ROW($B$7)</f>
+      <c r="B36" s="17">
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C36" s="22" t="s">
+      <c r="C36" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="D36" s="14" t="s">
+      <c r="D36" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="E36" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="F36" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="G36" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="H36" s="14" t="s">
-        <v>194</v>
+      <c r="E36" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="F36" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="G36" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="H36" s="20" t="s">
+        <v>189</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="J36" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="K36" s="45" t="s">
-        <v>264</v>
-      </c>
-      <c r="L36" s="14">
-        <v>6</v>
+        <v>280</v>
+      </c>
+      <c r="J36" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="K36" s="43" t="s">
+        <v>256</v>
+      </c>
+      <c r="L36" s="20">
+        <v>4</v>
       </c>
       <c r="M36" s="14">
         <f t="shared" si="1"/>
-        <v>60</v>
-      </c>
-      <c r="N36" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="O36" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P36" s="15" t="s">
-        <v>319</v>
-      </c>
-      <c r="Q36" s="15">
-        <f>P36*N36</f>
-        <v>1.04</v>
-      </c>
-      <c r="R36" s="14"/>
+        <v>40</v>
+      </c>
+      <c r="N36" s="20">
+        <v>50</v>
+      </c>
+      <c r="O36" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P36" s="21" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q36" s="21">
+        <f t="shared" ref="Q36" si="15">P36*N36</f>
+        <v>2.34</v>
+      </c>
+      <c r="R36" s="20"/>
     </row>
     <row r="37" spans="1:18">
       <c r="A37" s="1"/>
-      <c r="B37" s="17">
-        <f t="shared" si="0"/>
+      <c r="B37" s="16">
+        <f>ROW(B37) - ROW($B$7)</f>
         <v>30</v>
       </c>
-      <c r="C37" s="23" t="s">
+      <c r="C37" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="D37" s="20" t="s">
+      <c r="D37" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="E37" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="F37" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="G37" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="H37" s="20" t="s">
-        <v>194</v>
+      <c r="E37" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="F37" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="G37" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="H37" s="14" t="s">
+        <v>189</v>
       </c>
       <c r="I37" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="J37" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="K37" s="46" t="s">
-        <v>265</v>
-      </c>
-      <c r="L37" s="20">
-        <v>4</v>
+        <v>280</v>
+      </c>
+      <c r="J37" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="K37" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L37" s="14">
+        <v>1</v>
       </c>
       <c r="M37" s="14">
         <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="N37" s="20">
-        <v>50</v>
-      </c>
-      <c r="O37" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P37" s="21" t="s">
-        <v>320</v>
-      </c>
-      <c r="Q37" s="21">
-        <f t="shared" ref="Q37" si="16">P37*N37</f>
-        <v>2.34</v>
-      </c>
-      <c r="R37" s="20"/>
+        <v>10</v>
+      </c>
+      <c r="N37" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="O37" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P37" s="15" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q37" s="15">
+        <f>P37*N37</f>
+        <v>0.57799999999999996</v>
+      </c>
+      <c r="R37" s="14"/>
     </row>
     <row r="38" spans="1:18">
       <c r="A38" s="1"/>
-      <c r="B38" s="16">
-        <f>ROW(B38) - ROW($B$7)</f>
+      <c r="B38" s="17">
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C38" s="22" t="s">
+      <c r="C38" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="D38" s="14" t="s">
+      <c r="D38" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="E38" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="F38" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="G38" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="H38" s="14" t="s">
-        <v>194</v>
+      <c r="E38" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="F38" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="G38" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="H38" s="20" t="s">
+        <v>189</v>
       </c>
       <c r="I38" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="J38" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="K38" s="45" t="s">
-        <v>266</v>
-      </c>
-      <c r="L38" s="14">
+        <v>280</v>
+      </c>
+      <c r="J38" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="K38" s="43" t="s">
+        <v>258</v>
+      </c>
+      <c r="L38" s="20">
         <v>1</v>
       </c>
       <c r="M38" s="14">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N38" s="14" t="s">
-        <v>310</v>
-      </c>
-      <c r="O38" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P38" s="15" t="s">
-        <v>321</v>
-      </c>
-      <c r="Q38" s="15">
-        <f>P38*N38</f>
-        <v>0.57799999999999996</v>
-      </c>
-      <c r="R38" s="14"/>
+      <c r="N38" s="20">
+        <v>20</v>
+      </c>
+      <c r="O38" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P38" s="21" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q38" s="21">
+        <f t="shared" ref="Q38" si="16">P38*N38</f>
+        <v>1.002</v>
+      </c>
+      <c r="R38" s="20"/>
     </row>
     <row r="39" spans="1:18">
       <c r="A39" s="1"/>
-      <c r="B39" s="17">
-        <f t="shared" si="0"/>
+      <c r="B39" s="16">
+        <f>ROW(B39) - ROW($B$7)</f>
         <v>32</v>
       </c>
-      <c r="C39" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="D39" s="20" t="s">
+      <c r="C39" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D39" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="E39" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="F39" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="G39" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="H39" s="20" t="s">
-        <v>194</v>
+      <c r="E39" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="G39" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="H39" s="14" t="s">
+        <v>189</v>
       </c>
       <c r="I39" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="J39" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="K39" s="46" t="s">
-        <v>267</v>
-      </c>
-      <c r="L39" s="20">
+        <v>280</v>
+      </c>
+      <c r="J39" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="K39" s="42" t="s">
+        <v>259</v>
+      </c>
+      <c r="L39" s="14">
         <v>1</v>
       </c>
       <c r="M39" s="14">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N39" s="20">
-        <v>20</v>
-      </c>
-      <c r="O39" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P39" s="21" t="s">
-        <v>322</v>
-      </c>
-      <c r="Q39" s="21">
-        <f t="shared" ref="Q39" si="17">P39*N39</f>
-        <v>1.002</v>
-      </c>
-      <c r="R39" s="20"/>
+      <c r="N39" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="O39" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P39" s="15" t="s">
+        <v>312</v>
+      </c>
+      <c r="Q39" s="15">
+        <f>P39*N39</f>
+        <v>0.54500000000000004</v>
+      </c>
+      <c r="R39" s="14"/>
     </row>
     <row r="40" spans="1:18">
       <c r="A40" s="1"/>
-      <c r="B40" s="16">
-        <f>ROW(B40) - ROW($B$7)</f>
+      <c r="B40" s="17">
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C40" s="22" t="s">
+      <c r="C40" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D40" s="14" t="s">
+      <c r="D40" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="E40" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="F40" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="G40" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="H40" s="14" t="s">
-        <v>194</v>
+      <c r="E40" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="F40" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="G40" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="H40" s="20" t="s">
+        <v>189</v>
       </c>
       <c r="I40" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="J40" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="K40" s="45" t="s">
-        <v>268</v>
-      </c>
-      <c r="L40" s="14">
+        <v>280</v>
+      </c>
+      <c r="J40" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="K40" s="43" t="s">
+        <v>260</v>
+      </c>
+      <c r="L40" s="20">
         <v>1</v>
       </c>
       <c r="M40" s="14">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N40" s="14" t="s">
-        <v>312</v>
-      </c>
-      <c r="O40" s="47" t="s">
+      <c r="N40" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="O40" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P40" s="21" t="s">
         <v>313</v>
       </c>
-      <c r="P40" s="15" t="s">
-        <v>323</v>
-      </c>
-      <c r="Q40" s="15">
-        <f>P40*N40</f>
-        <v>0.54500000000000004</v>
-      </c>
-      <c r="R40" s="14"/>
+      <c r="Q40" s="21">
+        <f t="shared" ref="Q40" si="17">P40*N40</f>
+        <v>0.13</v>
+      </c>
+      <c r="R40" s="20"/>
     </row>
     <row r="41" spans="1:18">
       <c r="A41" s="1"/>
-      <c r="B41" s="17">
-        <f t="shared" si="0"/>
+      <c r="B41" s="16">
+        <f>ROW(B41) - ROW($B$7)</f>
         <v>34</v>
       </c>
-      <c r="C41" s="23" t="s">
+      <c r="C41" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D41" s="20" t="s">
+      <c r="D41" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="E41" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="F41" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="G41" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="H41" s="20" t="s">
-        <v>194</v>
+      <c r="E41" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="F41" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="G41" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="H41" s="14" t="s">
+        <v>189</v>
       </c>
       <c r="I41" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="J41" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="K41" s="42" t="s">
+        <v>261</v>
+      </c>
+      <c r="L41" s="14">
+        <v>1</v>
+      </c>
+      <c r="M41" s="14">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N41" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="O41" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P41" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="J41" s="20" t="s">
-        <v>236</v>
-      </c>
-      <c r="K41" s="46" t="s">
-        <v>269</v>
-      </c>
-      <c r="L41" s="20">
-        <v>1</v>
-      </c>
-      <c r="M41" s="14">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="N41" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="O41" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P41" s="21" t="s">
-        <v>324</v>
-      </c>
-      <c r="Q41" s="21">
-        <f t="shared" ref="Q41" si="18">P41*N41</f>
-        <v>0.13</v>
-      </c>
-      <c r="R41" s="20"/>
+      <c r="Q41" s="15">
+        <f>P41*N41</f>
+        <v>0.22</v>
+      </c>
+      <c r="R41" s="14"/>
     </row>
     <row r="42" spans="1:18">
       <c r="A42" s="1"/>
-      <c r="B42" s="16">
-        <f>ROW(B42) - ROW($B$7)</f>
+      <c r="B42" s="17">
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C42" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D42" s="14" t="s">
+      <c r="C42" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D42" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="E42" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="F42" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="G42" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="H42" s="14" t="s">
-        <v>194</v>
+      <c r="E42" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="F42" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="G42" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="H42" s="20" t="s">
+        <v>189</v>
       </c>
       <c r="I42" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="J42" s="14" t="s">
-        <v>237</v>
-      </c>
-      <c r="K42" s="45" t="s">
-        <v>270</v>
-      </c>
-      <c r="L42" s="14">
+        <v>280</v>
+      </c>
+      <c r="J42" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="K42" s="43" t="s">
+        <v>262</v>
+      </c>
+      <c r="L42" s="20">
         <v>1</v>
       </c>
       <c r="M42" s="14">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N42" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="O42" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P42" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="Q42" s="15">
-        <f>P42*N42</f>
-        <v>0.22</v>
-      </c>
-      <c r="R42" s="14"/>
+      <c r="N42" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="O42" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P42" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q42" s="21">
+        <f t="shared" ref="Q42" si="18">P42*N42</f>
+        <v>0.08</v>
+      </c>
+      <c r="R42" s="20"/>
     </row>
     <row r="43" spans="1:18">
       <c r="A43" s="1"/>
-      <c r="B43" s="17">
-        <f t="shared" si="0"/>
+      <c r="B43" s="16">
+        <f>ROW(B43) - ROW($B$7)</f>
         <v>36</v>
       </c>
-      <c r="C43" s="23" t="s">
+      <c r="C43" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="D43" s="20" t="s">
+      <c r="D43" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="E43" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="F43" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="G43" s="20" t="s">
-        <v>174</v>
-      </c>
-      <c r="H43" s="20" t="s">
-        <v>194</v>
+      <c r="E43" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="F43" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="G43" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H43" s="14" t="s">
+        <v>189</v>
       </c>
       <c r="I43" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="J43" s="20" t="s">
-        <v>238</v>
-      </c>
-      <c r="K43" s="46" t="s">
-        <v>271</v>
-      </c>
-      <c r="L43" s="20">
+        <v>280</v>
+      </c>
+      <c r="J43" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="K43" s="42" t="s">
+        <v>263</v>
+      </c>
+      <c r="L43" s="14">
         <v>1</v>
       </c>
       <c r="M43" s="14">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N43" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="O43" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P43" s="21" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q43" s="21">
-        <f t="shared" ref="Q43" si="19">P43*N43</f>
-        <v>0.08</v>
-      </c>
-      <c r="R43" s="20"/>
+      <c r="N43" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="O43" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P43" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q43" s="15">
+        <f>P43*N43</f>
+        <v>0.12</v>
+      </c>
+      <c r="R43" s="14"/>
     </row>
     <row r="44" spans="1:18">
       <c r="A44" s="1"/>
-      <c r="B44" s="16">
-        <f>ROW(B44) - ROW($B$7)</f>
+      <c r="B44" s="17">
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="C44" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="D44" s="14" t="s">
+      <c r="C44" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D44" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="E44" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="F44" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="G44" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="H44" s="14" t="s">
-        <v>194</v>
+      <c r="E44" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="F44" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="G44" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="H44" s="20" t="s">
+        <v>189</v>
       </c>
       <c r="I44" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="J44" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="K44" s="45" t="s">
-        <v>272</v>
-      </c>
-      <c r="L44" s="14">
+        <v>280</v>
+      </c>
+      <c r="J44" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="K44" s="43" t="s">
+        <v>264</v>
+      </c>
+      <c r="L44" s="20">
         <v>1</v>
       </c>
       <c r="M44" s="14">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N44" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="O44" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P44" s="15" t="s">
-        <v>326</v>
-      </c>
-      <c r="Q44" s="15">
-        <f>P44*N44</f>
-        <v>0.12</v>
-      </c>
-      <c r="R44" s="14"/>
+      <c r="N44" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="O44" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P44" s="21" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q44" s="21">
+        <f t="shared" ref="Q44" si="19">P44*N44</f>
+        <v>0.11</v>
+      </c>
+      <c r="R44" s="20"/>
     </row>
     <row r="45" spans="1:18">
       <c r="A45" s="1"/>
-      <c r="B45" s="17">
-        <f t="shared" si="0"/>
+      <c r="B45" s="16">
+        <f>ROW(B45) - ROW($B$7)</f>
         <v>38</v>
       </c>
-      <c r="C45" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="D45" s="20" t="s">
+      <c r="C45" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D45" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="E45" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="F45" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="G45" s="20" t="s">
-        <v>176</v>
-      </c>
-      <c r="H45" s="20" t="s">
-        <v>194</v>
+      <c r="E45" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="F45" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="G45" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="H45" s="14" t="s">
+        <v>189</v>
       </c>
       <c r="I45" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="J45" s="20" t="s">
-        <v>240</v>
-      </c>
-      <c r="K45" s="46" t="s">
-        <v>273</v>
-      </c>
-      <c r="L45" s="20">
+        <v>280</v>
+      </c>
+      <c r="J45" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="K45" s="42" t="s">
+        <v>265</v>
+      </c>
+      <c r="L45" s="14">
         <v>1</v>
       </c>
       <c r="M45" s="14">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N45" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="O45" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P45" s="21" t="s">
-        <v>327</v>
-      </c>
-      <c r="Q45" s="21">
-        <f t="shared" ref="Q45" si="20">P45*N45</f>
-        <v>0.11</v>
-      </c>
-      <c r="R45" s="20"/>
+      <c r="N45" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="O45" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P45" s="15" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q45" s="15">
+        <f>P45*N45</f>
+        <v>0.496</v>
+      </c>
+      <c r="R45" s="14"/>
     </row>
     <row r="46" spans="1:18">
       <c r="A46" s="1"/>
-      <c r="B46" s="16">
-        <f>ROW(B46) - ROW($B$7)</f>
+      <c r="B46" s="17">
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C46" s="22" t="s">
+      <c r="C46" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="D46" s="14" t="s">
+      <c r="D46" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="E46" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="F46" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="G46" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="H46" s="14" t="s">
-        <v>194</v>
+      <c r="E46" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="F46" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="G46" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="H46" s="20" t="s">
+        <v>189</v>
       </c>
       <c r="I46" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="J46" s="14" t="s">
-        <v>241</v>
-      </c>
-      <c r="K46" s="45" t="s">
-        <v>274</v>
-      </c>
-      <c r="L46" s="14">
+        <v>280</v>
+      </c>
+      <c r="J46" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="K46" s="43" t="s">
+        <v>266</v>
+      </c>
+      <c r="L46" s="20">
         <v>1</v>
       </c>
       <c r="M46" s="14">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N46" s="14" t="s">
-        <v>310</v>
-      </c>
-      <c r="O46" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P46" s="15" t="s">
-        <v>328</v>
-      </c>
-      <c r="Q46" s="15">
-        <f>P46*N46</f>
-        <v>0.496</v>
-      </c>
-      <c r="R46" s="14"/>
+      <c r="N46" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="O46" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P46" s="21" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q46" s="21">
+        <f t="shared" ref="Q46" si="20">P46*N46</f>
+        <v>0.95</v>
+      </c>
+      <c r="R46" s="20"/>
     </row>
     <row r="47" spans="1:18">
       <c r="A47" s="1"/>
-      <c r="B47" s="17">
+      <c r="B47" s="16">
+        <f>ROW(B47) - ROW($B$7)</f>
+        <v>40</v>
+      </c>
+      <c r="C47" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="E47" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="F47" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="G47" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="H47" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="I47" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="J47" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="K47" s="42" t="s">
+        <v>267</v>
+      </c>
+      <c r="L47" s="14">
+        <v>1</v>
+      </c>
+      <c r="M47" s="14">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N47" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="O47" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P47" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q47" s="15">
+        <f>P47*N47</f>
+        <v>0.48800000000000004</v>
+      </c>
+      <c r="R47" s="14"/>
+    </row>
+    <row r="48" spans="1:18" ht="24">
+      <c r="A48" s="1"/>
+      <c r="B48" s="17">
         <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="C48" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D48" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="E48" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="F48" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="G48" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="H48" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="I48" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="J48" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="K48" s="43" t="s">
+        <v>268</v>
+      </c>
+      <c r="L48" s="20">
+        <v>12</v>
+      </c>
+      <c r="M48" s="14">
+        <f t="shared" si="1"/>
+        <v>120</v>
+      </c>
+      <c r="N48" s="20">
+        <v>125</v>
+      </c>
+      <c r="O48" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P48" s="21" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q48" s="21">
+        <f t="shared" ref="Q48" si="21">P48*N48</f>
+        <v>22.512500000000003</v>
+      </c>
+      <c r="R48" s="20"/>
+    </row>
+    <row r="49" spans="1:18">
+      <c r="A49" s="1"/>
+      <c r="B49" s="16">
+        <f>ROW(B49) - ROW($B$7)</f>
+        <v>42</v>
+      </c>
+      <c r="C49" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D49" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E49" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="F49" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="G49" s="45" t="s">
+        <v>176</v>
+      </c>
+      <c r="H49" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="I49" s="14" t="s">
+        <v>328</v>
+      </c>
+      <c r="J49" s="14" t="s">
+        <v>327</v>
+      </c>
+      <c r="K49" s="42" t="s">
+        <v>264</v>
+      </c>
+      <c r="L49" s="14">
+        <v>6</v>
+      </c>
+      <c r="M49" s="14">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="N49" s="14">
+        <v>100</v>
+      </c>
+      <c r="O49" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P49" s="15" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q49" s="15">
+        <f>P49*N49</f>
+        <v>1.92</v>
+      </c>
+      <c r="R49" s="14"/>
+    </row>
+    <row r="50" spans="1:18" ht="24">
+      <c r="A50" s="1"/>
+      <c r="B50" s="17">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="C50" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D50" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E50" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="F50" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="G50" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="H50" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="I50" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="J50" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="K50" s="43" t="s">
+        <v>280</v>
+      </c>
+      <c r="L50" s="20">
+        <v>3</v>
+      </c>
+      <c r="M50" s="14">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="N50" s="20">
         <v>40</v>
       </c>
-      <c r="C47" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="D47" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="E47" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="F47" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="G47" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="H47" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="I47" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="J47" s="20" t="s">
-        <v>242</v>
-      </c>
-      <c r="K47" s="46" t="s">
-        <v>275</v>
-      </c>
-      <c r="L47" s="20">
-        <v>1</v>
-      </c>
-      <c r="M47" s="14">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="N47" s="20" t="s">
-        <v>312</v>
-      </c>
-      <c r="O47" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P47" s="21" t="s">
-        <v>329</v>
-      </c>
-      <c r="Q47" s="21">
-        <f t="shared" ref="Q47" si="21">P47*N47</f>
-        <v>0.95</v>
-      </c>
-      <c r="R47" s="20"/>
-    </row>
-    <row r="48" spans="1:18">
-      <c r="A48" s="1"/>
-      <c r="B48" s="16">
-        <f>ROW(B48) - ROW($B$7)</f>
-        <v>41</v>
-      </c>
-      <c r="C48" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="D48" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E48" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="F48" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="G48" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="H48" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="I48" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="J48" s="14" t="s">
-        <v>243</v>
-      </c>
-      <c r="K48" s="45" t="s">
-        <v>276</v>
-      </c>
-      <c r="L48" s="14">
-        <v>1</v>
-      </c>
-      <c r="M48" s="14">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="N48" s="14" t="s">
-        <v>310</v>
-      </c>
-      <c r="O48" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P48" s="15" t="s">
-        <v>330</v>
-      </c>
-      <c r="Q48" s="15">
-        <f>P48*N48</f>
-        <v>0.48800000000000004</v>
-      </c>
-      <c r="R48" s="14"/>
-    </row>
-    <row r="49" spans="1:18" ht="24">
-      <c r="A49" s="1"/>
-      <c r="B49" s="17">
-        <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
-      <c r="C49" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="D49" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="E49" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="F49" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="G49" s="20" t="s">
-        <v>180</v>
-      </c>
-      <c r="H49" s="20" t="s">
-        <v>202</v>
-      </c>
-      <c r="I49" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="J49" s="20" t="s">
-        <v>244</v>
-      </c>
-      <c r="K49" s="46" t="s">
-        <v>277</v>
-      </c>
-      <c r="L49" s="20">
-        <v>12</v>
-      </c>
-      <c r="M49" s="14">
-        <f t="shared" si="1"/>
-        <v>120</v>
-      </c>
-      <c r="N49" s="20">
-        <v>125</v>
-      </c>
-      <c r="O49" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P49" s="21" t="s">
-        <v>331</v>
-      </c>
-      <c r="Q49" s="21">
-        <f t="shared" ref="Q49" si="22">P49*N49</f>
-        <v>22.512500000000003</v>
-      </c>
-      <c r="R49" s="20"/>
-    </row>
-    <row r="50" spans="1:18">
-      <c r="A50" s="1"/>
-      <c r="B50" s="16">
-        <f>ROW(B50) - ROW($B$7)</f>
-        <v>43</v>
-      </c>
-      <c r="C50" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D50" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="E50" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="F50" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="G50" s="48" t="s">
-        <v>181</v>
-      </c>
-      <c r="H50" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="I50" s="14" t="s">
-        <v>339</v>
-      </c>
-      <c r="J50" s="14" t="s">
-        <v>338</v>
-      </c>
-      <c r="K50" s="45" t="s">
-        <v>273</v>
-      </c>
-      <c r="L50" s="14">
-        <v>6</v>
-      </c>
-      <c r="M50" s="14">
-        <f t="shared" si="1"/>
-        <v>60</v>
-      </c>
-      <c r="N50" s="14">
-        <v>100</v>
-      </c>
-      <c r="O50" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P50" s="15" t="s">
-        <v>332</v>
-      </c>
-      <c r="Q50" s="15">
-        <f>P50*N50</f>
-        <v>1.92</v>
-      </c>
-      <c r="R50" s="14"/>
-    </row>
-    <row r="51" spans="1:18" ht="24">
+      <c r="O50" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P50" s="21" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q50" s="21">
+        <f t="shared" ref="Q50:Q51" si="22">P50*N50</f>
+        <v>2.8079999999999998</v>
+      </c>
+      <c r="R50" s="20"/>
+    </row>
+    <row r="51" spans="1:18">
       <c r="A51" s="1"/>
       <c r="B51" s="17">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="C51" s="23" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D51" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="E51" s="20" t="s">
-        <v>116</v>
+        <v>372</v>
+      </c>
+      <c r="E51" s="43" t="s">
+        <v>373</v>
       </c>
       <c r="F51" s="20" t="s">
-        <v>290</v>
-      </c>
-      <c r="G51" s="20" t="s">
-        <v>144</v>
+        <v>281</v>
+      </c>
+      <c r="G51" s="43" t="s">
+        <v>374</v>
       </c>
       <c r="H51" s="20" t="s">
-        <v>194</v>
+        <v>280</v>
       </c>
       <c r="I51" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="J51" s="20" t="s">
-        <v>245</v>
-      </c>
-      <c r="K51" s="46" t="s">
-        <v>289</v>
-      </c>
-      <c r="L51" s="20">
+        <v>280</v>
+      </c>
+      <c r="J51" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="K51" s="43"/>
+      <c r="L51" s="14">
+        <v>1</v>
+      </c>
+      <c r="M51" s="14">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N51" s="14">
+        <v>11</v>
+      </c>
+      <c r="O51" s="44" t="s">
+        <v>280</v>
+      </c>
+      <c r="P51" s="21">
         <v>3</v>
       </c>
-      <c r="M51" s="14">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="N51" s="20">
-        <v>40</v>
-      </c>
-      <c r="O51" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P51" s="21" t="s">
-        <v>333</v>
-      </c>
       <c r="Q51" s="21">
-        <f t="shared" ref="Q51" si="23">P51*N51</f>
-        <v>2.8079999999999998</v>
-      </c>
-      <c r="R51" s="20"/>
+        <f t="shared" si="22"/>
+        <v>33</v>
+      </c>
+      <c r="R51" s="14"/>
     </row>
     <row r="52" spans="1:18" ht="24">
       <c r="A52" s="1"/>
@@ -4589,28 +4580,28 @@
         <v>24</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="G52" s="14" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="H52" s="14" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="I52" s="20" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J52" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="K52" s="46" t="s">
-        <v>289</v>
+        <v>237</v>
+      </c>
+      <c r="K52" s="43" t="s">
+        <v>280</v>
       </c>
       <c r="L52" s="14">
         <v>1</v>
@@ -4622,11 +4613,11 @@
       <c r="N52" s="14">
         <v>11</v>
       </c>
-      <c r="O52" s="47" t="s">
-        <v>313</v>
+      <c r="O52" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P52" s="15" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="Q52" s="15">
         <f>P52*N52</f>
@@ -4644,28 +4635,28 @@
         <v>24</v>
       </c>
       <c r="D53" s="20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F53" s="20" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="G53" s="20" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="H53" s="20" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I53" s="20" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J53" s="20" t="s">
-        <v>247</v>
-      </c>
-      <c r="K53" s="46" t="s">
-        <v>289</v>
+        <v>238</v>
+      </c>
+      <c r="K53" s="43" t="s">
+        <v>280</v>
       </c>
       <c r="L53" s="20">
         <v>1</v>
@@ -4677,14 +4668,14 @@
       <c r="N53" s="20">
         <v>15</v>
       </c>
-      <c r="O53" s="47" t="s">
-        <v>313</v>
+      <c r="O53" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P53" s="21" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="Q53" s="21">
-        <f t="shared" ref="Q53" si="24">P53*N53</f>
+        <f t="shared" ref="Q53" si="23">P53*N53</f>
         <v>3.528</v>
       </c>
       <c r="R53" s="20"/>
@@ -4699,28 +4690,28 @@
         <v>24</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G54" s="14" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="H54" s="14" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="I54" s="20" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J54" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="K54" s="46" t="s">
-        <v>289</v>
+        <v>239</v>
+      </c>
+      <c r="K54" s="43" t="s">
+        <v>280</v>
       </c>
       <c r="L54" s="14">
         <v>1</v>
@@ -4732,11 +4723,11 @@
       <c r="N54" s="14">
         <v>15</v>
       </c>
-      <c r="O54" s="47" t="s">
-        <v>313</v>
+      <c r="O54" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P54" s="15" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="Q54" s="15">
         <f>P54*N54</f>
@@ -4758,14 +4749,14 @@
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
       <c r="M55" s="1"/>
-      <c r="N55" s="43" t="s">
+      <c r="N55" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="O55" s="44"/>
-      <c r="P55" s="44"/>
+      <c r="O55" s="50"/>
+      <c r="P55" s="50"/>
       <c r="Q55" s="18">
         <f>SUM(Q8:Q54)</f>
-        <v>194.37659999999997</v>
+        <v>196.70939999999999</v>
       </c>
       <c r="R55" s="1"/>
     </row>
@@ -4783,14 +4774,14 @@
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
       <c r="M56" s="1"/>
-      <c r="N56" s="43" t="s">
+      <c r="N56" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="O56" s="44"/>
-      <c r="P56" s="44"/>
+      <c r="O56" s="50"/>
+      <c r="P56" s="50"/>
       <c r="Q56" s="19">
         <f>Q55/10</f>
-        <v>19.437659999999997</v>
+        <v>19.670939999999998</v>
       </c>
       <c r="R56" s="1"/>
     </row>
@@ -4823,33 +4814,33 @@
     <hyperlink ref="O26" r:id="rId17"/>
     <hyperlink ref="O27" r:id="rId18"/>
     <hyperlink ref="O28" r:id="rId19"/>
-    <hyperlink ref="O30" r:id="rId20"/>
-    <hyperlink ref="O31" r:id="rId21"/>
-    <hyperlink ref="O32" r:id="rId22"/>
-    <hyperlink ref="O34" r:id="rId23"/>
-    <hyperlink ref="O35" r:id="rId24"/>
-    <hyperlink ref="O36" r:id="rId25"/>
-    <hyperlink ref="O37" r:id="rId26"/>
-    <hyperlink ref="O38" r:id="rId27"/>
-    <hyperlink ref="O39" r:id="rId28"/>
-    <hyperlink ref="O40" r:id="rId29"/>
-    <hyperlink ref="O41" r:id="rId30"/>
-    <hyperlink ref="O42" r:id="rId31"/>
-    <hyperlink ref="O43" r:id="rId32"/>
-    <hyperlink ref="O44" r:id="rId33"/>
-    <hyperlink ref="O45" r:id="rId34"/>
-    <hyperlink ref="O46" r:id="rId35"/>
-    <hyperlink ref="O47" r:id="rId36"/>
-    <hyperlink ref="O48" r:id="rId37"/>
-    <hyperlink ref="O49" r:id="rId38"/>
-    <hyperlink ref="O51" r:id="rId39"/>
-    <hyperlink ref="O52" r:id="rId40"/>
-    <hyperlink ref="O53" r:id="rId41"/>
-    <hyperlink ref="O54" r:id="rId42"/>
-    <hyperlink ref="O9" r:id="rId43"/>
-    <hyperlink ref="O21" r:id="rId44"/>
-    <hyperlink ref="O29" r:id="rId45"/>
-    <hyperlink ref="O50" r:id="rId46"/>
+    <hyperlink ref="O32" r:id="rId20"/>
+    <hyperlink ref="O33" r:id="rId21"/>
+    <hyperlink ref="O34" r:id="rId22"/>
+    <hyperlink ref="O35" r:id="rId23"/>
+    <hyperlink ref="O36" r:id="rId24"/>
+    <hyperlink ref="O37" r:id="rId25"/>
+    <hyperlink ref="O38" r:id="rId26"/>
+    <hyperlink ref="O39" r:id="rId27"/>
+    <hyperlink ref="O40" r:id="rId28"/>
+    <hyperlink ref="O41" r:id="rId29"/>
+    <hyperlink ref="O42" r:id="rId30"/>
+    <hyperlink ref="O43" r:id="rId31"/>
+    <hyperlink ref="O44" r:id="rId32"/>
+    <hyperlink ref="O45" r:id="rId33"/>
+    <hyperlink ref="O46" r:id="rId34"/>
+    <hyperlink ref="O47" r:id="rId35"/>
+    <hyperlink ref="O48" r:id="rId36"/>
+    <hyperlink ref="O50" r:id="rId37"/>
+    <hyperlink ref="O52" r:id="rId38"/>
+    <hyperlink ref="O53" r:id="rId39"/>
+    <hyperlink ref="O54" r:id="rId40"/>
+    <hyperlink ref="O9" r:id="rId41"/>
+    <hyperlink ref="O21" r:id="rId42"/>
+    <hyperlink ref="O29" r:id="rId43"/>
+    <hyperlink ref="O49" r:id="rId44"/>
+    <hyperlink ref="O31" r:id="rId45"/>
+    <hyperlink ref="O30" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId47"/>
@@ -4890,14 +4881,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48"/>
+      <c r="R1" s="48"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1">
       <c r="A2" s="1"/>
@@ -4908,7 +4899,7 @@
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="40" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="3"/>
@@ -4932,7 +4923,7 @@
       </c>
       <c r="E3" s="27"/>
       <c r="F3" s="41" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="G3" s="29"/>
       <c r="H3" s="30"/>
@@ -5019,50 +5010,50 @@
         <v>25</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="M7" s="12" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="N7" s="12" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="O7" s="12" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="P7" s="12" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="Q7" s="12" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="R7" s="12" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" s="50" customFormat="1" ht="36">
-      <c r="A8" s="49"/>
+        <v>279</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" s="47" customFormat="1" ht="36">
+      <c r="A8" s="46"/>
       <c r="B8" s="16">
         <f>ROW(B8) - ROW($B$7)</f>
         <v>1</v>
@@ -5074,25 +5065,25 @@
         <v>26</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="K8" s="45" t="s">
-        <v>289</v>
+        <v>199</v>
+      </c>
+      <c r="K8" s="42" t="s">
+        <v>280</v>
       </c>
       <c r="L8" s="14">
         <v>2</v>
@@ -5104,11 +5095,11 @@
       <c r="N8" s="14">
         <v>2005</v>
       </c>
-      <c r="O8" s="47" t="s">
-        <v>313</v>
+      <c r="O8" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P8" s="15" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="Q8" s="15">
         <f>P8*N8</f>
@@ -5116,8 +5107,8 @@
       </c>
       <c r="R8" s="14"/>
     </row>
-    <row r="9" spans="1:18" s="50" customFormat="1">
-      <c r="A9" s="49"/>
+    <row r="9" spans="1:18" s="47" customFormat="1">
+      <c r="A9" s="46"/>
       <c r="B9" s="17">
         <f t="shared" ref="B9:B53" si="0">ROW(B9) - ROW($B$7)</f>
         <v>2</v>
@@ -5129,25 +5120,25 @@
         <v>27</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J9" s="20" t="s">
-        <v>207</v>
-      </c>
-      <c r="K9" s="46" t="s">
-        <v>249</v>
+        <v>200</v>
+      </c>
+      <c r="K9" s="43" t="s">
+        <v>240</v>
       </c>
       <c r="L9" s="20">
         <v>3</v>
@@ -5159,11 +5150,11 @@
       <c r="N9" s="20">
         <v>3005</v>
       </c>
-      <c r="O9" s="47" t="s">
-        <v>313</v>
+      <c r="O9" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P9" s="21" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="Q9" s="21">
         <f t="shared" ref="Q9" si="2">P9*N9</f>
@@ -5171,8 +5162,8 @@
       </c>
       <c r="R9" s="20"/>
     </row>
-    <row r="10" spans="1:18" s="50" customFormat="1" ht="36">
-      <c r="A10" s="49"/>
+    <row r="10" spans="1:18" s="47" customFormat="1" ht="36">
+      <c r="A10" s="46"/>
       <c r="B10" s="16">
         <f>ROW(B10) - ROW($B$7)</f>
         <v>3</v>
@@ -5184,25 +5175,25 @@
         <v>28</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="K10" s="45" t="s">
-        <v>250</v>
+        <v>201</v>
+      </c>
+      <c r="K10" s="42" t="s">
+        <v>241</v>
       </c>
       <c r="L10" s="14">
         <v>2</v>
@@ -5214,11 +5205,11 @@
       <c r="N10" s="14">
         <v>2002</v>
       </c>
-      <c r="O10" s="47" t="s">
-        <v>313</v>
+      <c r="O10" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P10" s="15" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="Q10" s="15">
         <f>P10*N10</f>
@@ -5226,8 +5217,8 @@
       </c>
       <c r="R10" s="14"/>
     </row>
-    <row r="11" spans="1:18" s="50" customFormat="1">
-      <c r="A11" s="49"/>
+    <row r="11" spans="1:18" s="47" customFormat="1">
+      <c r="A11" s="46"/>
       <c r="B11" s="17">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -5239,25 +5230,25 @@
         <v>29</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J11" s="20" t="s">
-        <v>209</v>
-      </c>
-      <c r="K11" s="46" t="s">
-        <v>251</v>
+        <v>202</v>
+      </c>
+      <c r="K11" s="43" t="s">
+        <v>242</v>
       </c>
       <c r="L11" s="20">
         <v>4</v>
@@ -5269,11 +5260,11 @@
       <c r="N11" s="20">
         <v>4005</v>
       </c>
-      <c r="O11" s="47" t="s">
-        <v>313</v>
+      <c r="O11" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P11" s="21" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="Q11" s="21">
         <f t="shared" ref="Q11" si="3">P11*N11</f>
@@ -5281,8 +5272,8 @@
       </c>
       <c r="R11" s="20"/>
     </row>
-    <row r="12" spans="1:18" s="50" customFormat="1">
-      <c r="A12" s="49"/>
+    <row r="12" spans="1:18" s="47" customFormat="1">
+      <c r="A12" s="46"/>
       <c r="B12" s="16">
         <f>ROW(B12) - ROW($B$7)</f>
         <v>5</v>
@@ -5294,25 +5285,25 @@
         <v>30</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>210</v>
-      </c>
-      <c r="K12" s="45" t="s">
-        <v>252</v>
+        <v>203</v>
+      </c>
+      <c r="K12" s="42" t="s">
+        <v>243</v>
       </c>
       <c r="L12" s="14">
         <v>1</v>
@@ -5324,11 +5315,11 @@
       <c r="N12" s="14">
         <v>1020</v>
       </c>
-      <c r="O12" s="47" t="s">
-        <v>313</v>
+      <c r="O12" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P12" s="15" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="Q12" s="15">
         <f>P12*N12</f>
@@ -5336,8 +5327,8 @@
       </c>
       <c r="R12" s="14"/>
     </row>
-    <row r="13" spans="1:18" s="50" customFormat="1" ht="36">
-      <c r="A13" s="49"/>
+    <row r="13" spans="1:18" s="47" customFormat="1" ht="36">
+      <c r="A13" s="46"/>
       <c r="B13" s="17">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -5349,25 +5340,25 @@
         <v>31</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J13" s="20" t="s">
-        <v>211</v>
-      </c>
-      <c r="K13" s="46" t="s">
-        <v>253</v>
+        <v>204</v>
+      </c>
+      <c r="K13" s="43" t="s">
+        <v>244</v>
       </c>
       <c r="L13" s="20">
         <v>1</v>
@@ -5379,11 +5370,11 @@
       <c r="N13" s="20">
         <v>1005</v>
       </c>
-      <c r="O13" s="47" t="s">
-        <v>313</v>
+      <c r="O13" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P13" s="21" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="Q13" s="21">
         <f t="shared" ref="Q13" si="4">P13*N13</f>
@@ -5391,8 +5382,8 @@
       </c>
       <c r="R13" s="20"/>
     </row>
-    <row r="14" spans="1:18" s="50" customFormat="1" ht="24">
-      <c r="A14" s="49"/>
+    <row r="14" spans="1:18" s="47" customFormat="1" ht="24">
+      <c r="A14" s="46"/>
       <c r="B14" s="16">
         <f>ROW(B14) - ROW($B$7)</f>
         <v>7</v>
@@ -5404,25 +5395,25 @@
         <v>32</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="K14" s="45" t="s">
-        <v>252</v>
+        <v>205</v>
+      </c>
+      <c r="K14" s="42" t="s">
+        <v>243</v>
       </c>
       <c r="L14" s="14">
         <v>1</v>
@@ -5434,11 +5425,11 @@
       <c r="N14" s="14">
         <v>5005</v>
       </c>
-      <c r="O14" s="47" t="s">
-        <v>313</v>
+      <c r="O14" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P14" s="15" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="Q14" s="15">
         <f>P14*N14</f>
@@ -5446,8 +5437,8 @@
       </c>
       <c r="R14" s="14"/>
     </row>
-    <row r="15" spans="1:18" s="50" customFormat="1" ht="25.5">
-      <c r="A15" s="49"/>
+    <row r="15" spans="1:18" s="47" customFormat="1" ht="25.5">
+      <c r="A15" s="46"/>
       <c r="B15" s="17">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -5459,25 +5450,25 @@
         <v>33</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J15" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="K15" s="46" t="s">
-        <v>254</v>
+        <v>206</v>
+      </c>
+      <c r="K15" s="43" t="s">
+        <v>245</v>
       </c>
       <c r="L15" s="20">
         <v>1</v>
@@ -5489,11 +5480,11 @@
       <c r="N15" s="20">
         <v>1005</v>
       </c>
-      <c r="O15" s="47" t="s">
-        <v>313</v>
+      <c r="O15" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P15" s="21" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="Q15" s="21">
         <f t="shared" ref="Q15" si="5">P15*N15</f>
@@ -5501,8 +5492,8 @@
       </c>
       <c r="R15" s="20"/>
     </row>
-    <row r="16" spans="1:18" s="50" customFormat="1">
-      <c r="A16" s="49"/>
+    <row r="16" spans="1:18" s="47" customFormat="1">
+      <c r="A16" s="46"/>
       <c r="B16" s="16">
         <f>ROW(B16) - ROW($B$7)</f>
         <v>9</v>
@@ -5514,25 +5505,25 @@
         <v>34</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="K16" s="45" t="s">
-        <v>255</v>
+        <v>207</v>
+      </c>
+      <c r="K16" s="42" t="s">
+        <v>246</v>
       </c>
       <c r="L16" s="14">
         <v>1</v>
@@ -5544,11 +5535,11 @@
       <c r="N16" s="14">
         <v>1100</v>
       </c>
-      <c r="O16" s="47" t="s">
-        <v>313</v>
+      <c r="O16" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P16" s="15" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="Q16" s="15">
         <f>P16*N16</f>
@@ -5556,8 +5547,8 @@
       </c>
       <c r="R16" s="14"/>
     </row>
-    <row r="17" spans="1:18" s="50" customFormat="1">
-      <c r="A17" s="49"/>
+    <row r="17" spans="1:18" s="47" customFormat="1">
+      <c r="A17" s="46"/>
       <c r="B17" s="17">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -5569,25 +5560,25 @@
         <v>35</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J17" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="K17" s="46" t="s">
-        <v>256</v>
+        <v>208</v>
+      </c>
+      <c r="K17" s="43" t="s">
+        <v>247</v>
       </c>
       <c r="L17" s="20">
         <v>2</v>
@@ -5599,11 +5590,11 @@
       <c r="N17" s="20">
         <v>2020</v>
       </c>
-      <c r="O17" s="47" t="s">
-        <v>313</v>
+      <c r="O17" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P17" s="21" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="Q17" s="21">
         <f t="shared" ref="Q17" si="6">P17*N17</f>
@@ -5611,8 +5602,8 @@
       </c>
       <c r="R17" s="20"/>
     </row>
-    <row r="18" spans="1:18" s="50" customFormat="1">
-      <c r="A18" s="49"/>
+    <row r="18" spans="1:18" s="47" customFormat="1">
+      <c r="A18" s="46"/>
       <c r="B18" s="16">
         <f>ROW(B18) - ROW($B$7)</f>
         <v>11</v>
@@ -5624,25 +5615,25 @@
         <v>36</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>216</v>
-      </c>
-      <c r="K18" s="45" t="s">
-        <v>257</v>
+        <v>209</v>
+      </c>
+      <c r="K18" s="42" t="s">
+        <v>248</v>
       </c>
       <c r="L18" s="14">
         <v>1</v>
@@ -5654,11 +5645,11 @@
       <c r="N18" s="14">
         <v>1050</v>
       </c>
-      <c r="O18" s="47" t="s">
-        <v>313</v>
+      <c r="O18" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P18" s="15" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="Q18" s="15">
         <f>P18*N18</f>
@@ -5666,8 +5657,8 @@
       </c>
       <c r="R18" s="14"/>
     </row>
-    <row r="19" spans="1:18" s="50" customFormat="1">
-      <c r="A19" s="49"/>
+    <row r="19" spans="1:18" s="47" customFormat="1">
+      <c r="A19" s="46"/>
       <c r="B19" s="17">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -5679,25 +5670,25 @@
         <v>37</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J19" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="K19" s="46" t="s">
-        <v>258</v>
+        <v>210</v>
+      </c>
+      <c r="K19" s="43" t="s">
+        <v>249</v>
       </c>
       <c r="L19" s="20">
         <v>1</v>
@@ -5709,11 +5700,11 @@
       <c r="N19" s="20">
         <v>1100</v>
       </c>
-      <c r="O19" s="47" t="s">
-        <v>313</v>
+      <c r="O19" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P19" s="21" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" ref="Q19" si="7">P19*N19</f>
@@ -5721,8 +5712,8 @@
       </c>
       <c r="R19" s="20"/>
     </row>
-    <row r="20" spans="1:18" s="50" customFormat="1" ht="24">
-      <c r="A20" s="49"/>
+    <row r="20" spans="1:18" s="47" customFormat="1" ht="24">
+      <c r="A20" s="46"/>
       <c r="B20" s="16">
         <f>ROW(B20) - ROW($B$7)</f>
         <v>13</v>
@@ -5734,25 +5725,25 @@
         <v>38</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>218</v>
-      </c>
-      <c r="K20" s="45" t="s">
-        <v>259</v>
+        <v>211</v>
+      </c>
+      <c r="K20" s="42" t="s">
+        <v>250</v>
       </c>
       <c r="L20" s="14">
         <v>3</v>
@@ -5764,11 +5755,11 @@
       <c r="N20" s="14">
         <v>3002</v>
       </c>
-      <c r="O20" s="47" t="s">
-        <v>313</v>
+      <c r="O20" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P20" s="15" t="s">
-        <v>356</v>
+        <v>345</v>
       </c>
       <c r="Q20" s="15">
         <f>P20*N20</f>
@@ -5776,8 +5767,8 @@
       </c>
       <c r="R20" s="14"/>
     </row>
-    <row r="21" spans="1:18" s="50" customFormat="1" ht="30">
-      <c r="A21" s="49"/>
+    <row r="21" spans="1:18" s="47" customFormat="1" ht="30">
+      <c r="A21" s="46"/>
       <c r="B21" s="17">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -5789,25 +5780,25 @@
         <v>39</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G21" s="20" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J21" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="K21" s="46" t="s">
-        <v>260</v>
+        <v>280</v>
+      </c>
+      <c r="K21" s="43" t="s">
+        <v>251</v>
       </c>
       <c r="L21" s="20">
         <v>6</v>
@@ -5819,8 +5810,8 @@
       <c r="N21" s="20">
         <v>6002</v>
       </c>
-      <c r="O21" s="47" t="s">
-        <v>337</v>
+      <c r="O21" s="44" t="s">
+        <v>326</v>
       </c>
       <c r="P21" s="21">
         <v>1.4E-2</v>
@@ -5831,8 +5822,8 @@
       </c>
       <c r="R21" s="20"/>
     </row>
-    <row r="22" spans="1:18" s="50" customFormat="1" ht="36">
-      <c r="A22" s="49"/>
+    <row r="22" spans="1:18" s="47" customFormat="1" ht="36">
+      <c r="A22" s="46"/>
       <c r="B22" s="16">
         <f>ROW(B22) - ROW($B$7)</f>
         <v>15</v>
@@ -5844,25 +5835,25 @@
         <v>40</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>219</v>
-      </c>
-      <c r="K22" s="45" t="s">
-        <v>289</v>
+        <v>212</v>
+      </c>
+      <c r="K22" s="42" t="s">
+        <v>280</v>
       </c>
       <c r="L22" s="14">
         <v>1</v>
@@ -5874,11 +5865,11 @@
       <c r="N22" s="14">
         <v>1002</v>
       </c>
-      <c r="O22" s="47" t="s">
-        <v>313</v>
+      <c r="O22" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P22" s="15" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="Q22" s="15">
         <f>P22*N22</f>
@@ -5886,8 +5877,8 @@
       </c>
       <c r="R22" s="14"/>
     </row>
-    <row r="23" spans="1:18" s="50" customFormat="1">
-      <c r="A23" s="49"/>
+    <row r="23" spans="1:18" s="47" customFormat="1">
+      <c r="A23" s="46"/>
       <c r="B23" s="17">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -5899,25 +5890,25 @@
         <v>41</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="H23" s="20" t="s">
         <v>11</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J23" s="20" t="s">
-        <v>220</v>
-      </c>
-      <c r="K23" s="46" t="s">
-        <v>261</v>
+        <v>213</v>
+      </c>
+      <c r="K23" s="43" t="s">
+        <v>252</v>
       </c>
       <c r="L23" s="20">
         <v>1</v>
@@ -5929,11 +5920,11 @@
       <c r="N23" s="20">
         <v>1020</v>
       </c>
-      <c r="O23" s="47" t="s">
-        <v>313</v>
+      <c r="O23" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P23" s="21" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="Q23" s="21">
         <f t="shared" ref="Q23" si="9">P23*N23</f>
@@ -5941,8 +5932,8 @@
       </c>
       <c r="R23" s="20"/>
     </row>
-    <row r="24" spans="1:18" s="50" customFormat="1">
-      <c r="A24" s="49"/>
+    <row r="24" spans="1:18" s="47" customFormat="1">
+      <c r="A24" s="46"/>
       <c r="B24" s="16">
         <f>ROW(B24) - ROW($B$7)</f>
         <v>17</v>
@@ -5954,25 +5945,25 @@
         <v>42</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="H24" s="14" t="s">
         <v>11</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>221</v>
-      </c>
-      <c r="K24" s="45" t="s">
-        <v>289</v>
+        <v>214</v>
+      </c>
+      <c r="K24" s="42" t="s">
+        <v>280</v>
       </c>
       <c r="L24" s="14">
         <v>1</v>
@@ -5984,11 +5975,11 @@
       <c r="N24" s="14">
         <v>1010</v>
       </c>
-      <c r="O24" s="47" t="s">
-        <v>313</v>
+      <c r="O24" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P24" s="15" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="Q24" s="15">
         <f>P24*N24</f>
@@ -5996,8 +5987,8 @@
       </c>
       <c r="R24" s="14"/>
     </row>
-    <row r="25" spans="1:18" s="50" customFormat="1">
-      <c r="A25" s="49"/>
+    <row r="25" spans="1:18" s="47" customFormat="1">
+      <c r="A25" s="46"/>
       <c r="B25" s="17">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -6009,25 +6000,25 @@
         <v>43</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="H25" s="20" t="s">
         <v>11</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J25" s="20" t="s">
-        <v>222</v>
-      </c>
-      <c r="K25" s="45" t="s">
-        <v>289</v>
+        <v>215</v>
+      </c>
+      <c r="K25" s="42" t="s">
+        <v>280</v>
       </c>
       <c r="L25" s="20">
         <v>1</v>
@@ -6039,11 +6030,11 @@
       <c r="N25" s="20">
         <v>1005</v>
       </c>
-      <c r="O25" s="47" t="s">
-        <v>313</v>
+      <c r="O25" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P25" s="21" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="Q25" s="21">
         <f t="shared" ref="Q25" si="10">P25*N25</f>
@@ -6051,8 +6042,8 @@
       </c>
       <c r="R25" s="20"/>
     </row>
-    <row r="26" spans="1:18" s="50" customFormat="1">
-      <c r="A26" s="49"/>
+    <row r="26" spans="1:18" s="47" customFormat="1">
+      <c r="A26" s="46"/>
       <c r="B26" s="16">
         <f>ROW(B26) - ROW($B$7)</f>
         <v>19</v>
@@ -6064,25 +6055,25 @@
         <v>44</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F26" s="20" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="K26" s="45" t="s">
-        <v>289</v>
+        <v>216</v>
+      </c>
+      <c r="K26" s="42" t="s">
+        <v>280</v>
       </c>
       <c r="L26" s="14">
         <v>1</v>
@@ -6094,11 +6085,11 @@
       <c r="N26" s="14">
         <v>1005</v>
       </c>
-      <c r="O26" s="47" t="s">
-        <v>313</v>
+      <c r="O26" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P26" s="15" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="Q26" s="15">
         <f>P26*N26</f>
@@ -6106,8 +6097,8 @@
       </c>
       <c r="R26" s="14"/>
     </row>
-    <row r="27" spans="1:18" s="50" customFormat="1">
-      <c r="A27" s="49"/>
+    <row r="27" spans="1:18" s="47" customFormat="1">
+      <c r="A27" s="46"/>
       <c r="B27" s="17">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -6119,25 +6110,25 @@
         <v>45</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J27" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="K27" s="45" t="s">
-        <v>289</v>
+        <v>217</v>
+      </c>
+      <c r="K27" s="42" t="s">
+        <v>280</v>
       </c>
       <c r="L27" s="20">
         <v>4</v>
@@ -6149,11 +6140,11 @@
       <c r="N27" s="20">
         <v>4010</v>
       </c>
-      <c r="O27" s="47" t="s">
-        <v>313</v>
+      <c r="O27" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P27" s="21" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="Q27" s="21">
         <f t="shared" ref="Q27" si="11">P27*N27</f>
@@ -6161,8 +6152,8 @@
       </c>
       <c r="R27" s="20"/>
     </row>
-    <row r="28" spans="1:18" s="50" customFormat="1">
-      <c r="A28" s="49"/>
+    <row r="28" spans="1:18" s="47" customFormat="1">
+      <c r="A28" s="46"/>
       <c r="B28" s="16">
         <f>ROW(B28) - ROW($B$7)</f>
         <v>21</v>
@@ -6174,25 +6165,25 @@
         <v>46</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F28" s="20" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="K28" s="45" t="s">
-        <v>289</v>
+        <v>218</v>
+      </c>
+      <c r="K28" s="42" t="s">
+        <v>280</v>
       </c>
       <c r="L28" s="14">
         <v>1</v>
@@ -6204,11 +6195,11 @@
       <c r="N28" s="14">
         <v>1002</v>
       </c>
-      <c r="O28" s="47" t="s">
-        <v>313</v>
+      <c r="O28" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P28" s="15" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="Q28" s="15">
         <f>P28*N28</f>
@@ -6216,8 +6207,8 @@
       </c>
       <c r="R28" s="14"/>
     </row>
-    <row r="29" spans="1:18" s="50" customFormat="1" ht="30">
-      <c r="A29" s="49"/>
+    <row r="29" spans="1:18" s="47" customFormat="1" ht="30">
+      <c r="A29" s="46"/>
       <c r="B29" s="17">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -6229,25 +6220,25 @@
         <v>47</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="G29" s="20" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I29" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J29" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="K29" s="45" t="s">
-        <v>289</v>
+        <v>280</v>
+      </c>
+      <c r="K29" s="42" t="s">
+        <v>280</v>
       </c>
       <c r="L29" s="20">
         <v>1</v>
@@ -6259,8 +6250,8 @@
       <c r="N29" s="20">
         <v>1002</v>
       </c>
-      <c r="O29" s="47" t="s">
-        <v>337</v>
+      <c r="O29" s="44" t="s">
+        <v>326</v>
       </c>
       <c r="P29" s="21">
         <v>0.91935</v>
@@ -6271,8 +6262,8 @@
       </c>
       <c r="R29" s="20"/>
     </row>
-    <row r="30" spans="1:18" s="50" customFormat="1" ht="60">
-      <c r="A30" s="49"/>
+    <row r="30" spans="1:18" s="47" customFormat="1" ht="24">
+      <c r="A30" s="46"/>
       <c r="B30" s="16">
         <f>ROW(B30) - ROW($B$7)</f>
         <v>23</v>
@@ -6283,26 +6274,26 @@
       <c r="D30" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E30" s="14" t="s">
-        <v>96</v>
+      <c r="E30" s="42" t="s">
+        <v>375</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>290</v>
-      </c>
-      <c r="G30" s="14" t="s">
-        <v>135</v>
+        <v>281</v>
+      </c>
+      <c r="G30" s="42" t="s">
+        <v>376</v>
       </c>
       <c r="H30" s="14" t="s">
-        <v>198</v>
+        <v>377</v>
       </c>
       <c r="I30" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>226</v>
-      </c>
-      <c r="K30" s="45" t="s">
-        <v>289</v>
+        <v>380</v>
+      </c>
+      <c r="K30" s="42" t="s">
+        <v>280</v>
       </c>
       <c r="L30" s="14">
         <v>1</v>
@@ -6314,20 +6305,20 @@
       <c r="N30" s="14">
         <v>1005</v>
       </c>
-      <c r="O30" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P30" s="15" t="s">
-        <v>365</v>
+      <c r="O30" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P30" s="15">
+        <v>0.1072</v>
       </c>
       <c r="Q30" s="15">
         <f>P30*N30</f>
-        <v>91.354500000000002</v>
+        <v>107.736</v>
       </c>
       <c r="R30" s="14"/>
     </row>
-    <row r="31" spans="1:18" s="50" customFormat="1" ht="48">
-      <c r="A31" s="49"/>
+    <row r="31" spans="1:18" s="47" customFormat="1" ht="48">
+      <c r="A31" s="46"/>
       <c r="B31" s="17">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -6338,26 +6329,26 @@
       <c r="D31" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="E31" s="20" t="s">
-        <v>97</v>
+      <c r="E31" s="43" t="s">
+        <v>378</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>290</v>
-      </c>
-      <c r="G31" s="20" t="s">
-        <v>165</v>
+        <v>281</v>
+      </c>
+      <c r="G31" s="43" t="s">
+        <v>379</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>199</v>
+        <v>377</v>
       </c>
       <c r="I31" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J31" s="20" t="s">
-        <v>227</v>
-      </c>
-      <c r="K31" s="45" t="s">
-        <v>289</v>
+        <v>381</v>
+      </c>
+      <c r="K31" s="42" t="s">
+        <v>280</v>
       </c>
       <c r="L31" s="20">
         <v>1</v>
@@ -6369,20 +6360,20 @@
       <c r="N31" s="20">
         <v>1002</v>
       </c>
-      <c r="O31" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P31" s="21" t="s">
-        <v>366</v>
+      <c r="O31" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P31" s="21">
+        <v>0.46489999999999998</v>
       </c>
       <c r="Q31" s="21">
         <f t="shared" ref="Q31" si="13">P31*N31</f>
-        <v>222.34379999999999</v>
+        <v>465.82979999999998</v>
       </c>
       <c r="R31" s="20"/>
     </row>
-    <row r="32" spans="1:18" s="50" customFormat="1" ht="24">
-      <c r="A32" s="49"/>
+    <row r="32" spans="1:18" s="47" customFormat="1" ht="24">
+      <c r="A32" s="46"/>
       <c r="B32" s="16">
         <f>ROW(B32) - ROW($B$7)</f>
         <v>25</v>
@@ -6394,25 +6385,25 @@
         <v>50</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H32" s="14" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="I32" s="14" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>228</v>
-      </c>
-      <c r="K32" s="45" t="s">
-        <v>262</v>
+        <v>219</v>
+      </c>
+      <c r="K32" s="42" t="s">
+        <v>253</v>
       </c>
       <c r="L32" s="14">
         <v>6</v>
@@ -6424,11 +6415,11 @@
       <c r="N32" s="14">
         <v>6005</v>
       </c>
-      <c r="O32" s="47" t="s">
-        <v>313</v>
+      <c r="O32" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P32" s="15" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="Q32" s="15">
         <f>P32*N32</f>
@@ -6436,1051 +6427,1051 @@
       </c>
       <c r="R32" s="14"/>
     </row>
-    <row r="33" spans="1:18" s="50" customFormat="1">
-      <c r="A33" s="49"/>
-      <c r="B33" s="17">
+    <row r="33" spans="1:18" s="47" customFormat="1" ht="24">
+      <c r="A33" s="46"/>
+      <c r="B33" s="16">
+        <f>ROW(B33) - ROW($B$7)</f>
+        <v>26</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="H33" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="I33" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="J33" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="K33" s="43" t="s">
+        <v>280</v>
+      </c>
+      <c r="L33" s="14">
+        <v>1</v>
+      </c>
+      <c r="M33" s="14">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N33" s="14">
+        <v>1002</v>
+      </c>
+      <c r="O33" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P33" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q33" s="15">
+        <f>P33*N33</f>
+        <v>473.6454</v>
+      </c>
+      <c r="R33" s="14"/>
+    </row>
+    <row r="34" spans="1:18" s="47" customFormat="1" ht="25.5">
+      <c r="A34" s="46"/>
+      <c r="B34" s="17">
         <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="C33" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="D33" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="E33" s="46" t="s">
-        <v>289</v>
-      </c>
-      <c r="F33" s="20" t="s">
-        <v>290</v>
-      </c>
-      <c r="G33" s="46" t="s">
-        <v>289</v>
-      </c>
-      <c r="H33" s="20"/>
-      <c r="I33" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="J33" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="K33" s="46" t="s">
-        <v>289</v>
-      </c>
-      <c r="L33" s="20">
+        <v>27</v>
+      </c>
+      <c r="C34" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="F34" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="G34" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="H34" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="I34" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="J34" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="K34" s="43" t="s">
+        <v>254</v>
+      </c>
+      <c r="L34" s="20">
+        <v>3</v>
+      </c>
+      <c r="M34" s="14">
+        <f t="shared" si="1"/>
+        <v>3000</v>
+      </c>
+      <c r="N34" s="20">
+        <v>3010</v>
+      </c>
+      <c r="O34" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P34" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q34" s="21">
+        <f t="shared" ref="Q34" si="14">P34*N34</f>
+        <v>119.497</v>
+      </c>
+      <c r="R34" s="20"/>
+    </row>
+    <row r="35" spans="1:18" s="47" customFormat="1">
+      <c r="A35" s="46"/>
+      <c r="B35" s="16">
+        <f>ROW(B35) - ROW($B$7)</f>
+        <v>28</v>
+      </c>
+      <c r="C35" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="H35" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="I35" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="J35" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="K35" s="42" t="s">
+        <v>255</v>
+      </c>
+      <c r="L35" s="14">
+        <v>6</v>
+      </c>
+      <c r="M35" s="14">
+        <f t="shared" si="1"/>
+        <v>6000</v>
+      </c>
+      <c r="N35" s="14">
+        <v>6050</v>
+      </c>
+      <c r="O35" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P35" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q35" s="15">
+        <f>P35*N35</f>
+        <v>38.115000000000002</v>
+      </c>
+      <c r="R35" s="14"/>
+    </row>
+    <row r="36" spans="1:18" s="47" customFormat="1">
+      <c r="A36" s="46"/>
+      <c r="B36" s="17">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="C36" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D36" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="F36" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="G36" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="H36" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="I36" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="J36" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="K36" s="43" t="s">
+        <v>256</v>
+      </c>
+      <c r="L36" s="20">
+        <v>4</v>
+      </c>
+      <c r="M36" s="14">
+        <f t="shared" si="1"/>
+        <v>4000</v>
+      </c>
+      <c r="N36" s="20">
+        <v>4010</v>
+      </c>
+      <c r="O36" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P36" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="Q36" s="21">
+        <f t="shared" ref="Q36" si="15">P36*N36</f>
+        <v>120.70099999999999</v>
+      </c>
+      <c r="R36" s="20"/>
+    </row>
+    <row r="37" spans="1:18" s="47" customFormat="1">
+      <c r="A37" s="46"/>
+      <c r="B37" s="16">
+        <f>ROW(B37) - ROW($B$7)</f>
+        <v>30</v>
+      </c>
+      <c r="C37" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="F37" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="G37" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="H37" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="I37" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="J37" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="K37" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L37" s="14">
         <v>1</v>
       </c>
-      <c r="M33" s="14">
+      <c r="M37" s="14">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="N33" s="20">
-        <v>1002</v>
-      </c>
-      <c r="O33" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="P33" s="21">
-        <v>0.93</v>
-      </c>
-      <c r="Q33" s="21">
-        <f t="shared" ref="Q33" si="14">P33*N33</f>
-        <v>931.86</v>
-      </c>
-      <c r="R33" s="20"/>
-    </row>
-    <row r="34" spans="1:18" s="50" customFormat="1" ht="24">
-      <c r="A34" s="49"/>
-      <c r="B34" s="16">
-        <f>ROW(B34) - ROW($B$7)</f>
-        <v>27</v>
-      </c>
-      <c r="C34" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="E34" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="F34" s="14" t="s">
+      <c r="N37" s="14">
+        <v>1020</v>
+      </c>
+      <c r="O37" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P37" s="15" t="s">
+        <v>359</v>
+      </c>
+      <c r="Q37" s="15">
+        <f>P37*N37</f>
+        <v>19.686</v>
+      </c>
+      <c r="R37" s="14"/>
+    </row>
+    <row r="38" spans="1:18" s="47" customFormat="1">
+      <c r="A38" s="46"/>
+      <c r="B38" s="17">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="C38" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D38" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="F38" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="G34" s="14" t="s">
+      <c r="G38" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="H38" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="I38" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="J38" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="K38" s="43" t="s">
+        <v>258</v>
+      </c>
+      <c r="L38" s="20">
+        <v>1</v>
+      </c>
+      <c r="M38" s="14">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N38" s="20">
+        <v>1010</v>
+      </c>
+      <c r="O38" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P38" s="21" t="s">
+        <v>360</v>
+      </c>
+      <c r="Q38" s="21">
+        <f t="shared" ref="Q38" si="16">P38*N38</f>
+        <v>32.723999999999997</v>
+      </c>
+      <c r="R38" s="20"/>
+    </row>
+    <row r="39" spans="1:18" s="47" customFormat="1">
+      <c r="A39" s="46"/>
+      <c r="B39" s="16">
+        <f>ROW(B39) - ROW($B$7)</f>
+        <v>32</v>
+      </c>
+      <c r="C39" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="G39" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="H34" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="I34" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="J34" s="14" t="s">
+      <c r="H39" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="I39" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="J39" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="K39" s="42" t="s">
+        <v>259</v>
+      </c>
+      <c r="L39" s="14">
+        <v>1</v>
+      </c>
+      <c r="M39" s="14">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N39" s="14">
+        <v>1050</v>
+      </c>
+      <c r="O39" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P39" s="15" t="s">
+        <v>361</v>
+      </c>
+      <c r="Q39" s="15">
+        <f>P39*N39</f>
+        <v>9.0299999999999994</v>
+      </c>
+      <c r="R39" s="14"/>
+    </row>
+    <row r="40" spans="1:18" s="47" customFormat="1">
+      <c r="A40" s="46"/>
+      <c r="B40" s="17">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="C40" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D40" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="F40" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="G40" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="H40" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="I40" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="J40" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="K40" s="43" t="s">
+        <v>260</v>
+      </c>
+      <c r="L40" s="20">
+        <v>1</v>
+      </c>
+      <c r="M40" s="14">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N40" s="20">
+        <v>1100</v>
+      </c>
+      <c r="O40" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P40" s="21" t="s">
+        <v>362</v>
+      </c>
+      <c r="Q40" s="21">
+        <f t="shared" ref="Q40" si="17">P40*N40</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="R40" s="20"/>
+    </row>
+    <row r="41" spans="1:18" s="47" customFormat="1">
+      <c r="A41" s="46"/>
+      <c r="B41" s="16">
+        <f>ROW(B41) - ROW($B$7)</f>
+        <v>34</v>
+      </c>
+      <c r="C41" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D41" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="F41" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="G41" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="H41" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="I41" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="J41" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="K41" s="42" t="s">
+        <v>261</v>
+      </c>
+      <c r="L41" s="14">
+        <v>1</v>
+      </c>
+      <c r="M41" s="14">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N41" s="14">
+        <v>1100</v>
+      </c>
+      <c r="O41" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P41" s="15" t="s">
+        <v>341</v>
+      </c>
+      <c r="Q41" s="15">
+        <f>P41*N41</f>
+        <v>1.8699999999999999</v>
+      </c>
+      <c r="R41" s="14"/>
+    </row>
+    <row r="42" spans="1:18" s="47" customFormat="1">
+      <c r="A42" s="46"/>
+      <c r="B42" s="17">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="C42" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D42" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="E42" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="F42" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="G42" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="H42" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="I42" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="J42" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="K34" s="46" t="s">
-        <v>289</v>
-      </c>
-      <c r="L34" s="14">
+      <c r="K42" s="43" t="s">
+        <v>262</v>
+      </c>
+      <c r="L42" s="20">
         <v>1</v>
       </c>
-      <c r="M34" s="14">
+      <c r="M42" s="14">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="N34" s="14">
-        <v>1002</v>
-      </c>
-      <c r="O34" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P34" s="15" t="s">
+      <c r="N42" s="20">
+        <v>1100</v>
+      </c>
+      <c r="O42" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P42" s="21" t="s">
+        <v>363</v>
+      </c>
+      <c r="Q42" s="21">
+        <f t="shared" ref="Q42" si="18">P42*N42</f>
+        <v>0.65999999999999992</v>
+      </c>
+      <c r="R42" s="20"/>
+    </row>
+    <row r="43" spans="1:18" s="47" customFormat="1">
+      <c r="A43" s="46"/>
+      <c r="B43" s="16">
+        <f>ROW(B43) - ROW($B$7)</f>
+        <v>36</v>
+      </c>
+      <c r="C43" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="F43" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="G43" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H43" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="I43" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="J43" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="K43" s="42" t="s">
+        <v>263</v>
+      </c>
+      <c r="L43" s="14">
+        <v>1</v>
+      </c>
+      <c r="M43" s="14">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N43" s="14">
+        <v>1100</v>
+      </c>
+      <c r="O43" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P43" s="15" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q43" s="15">
+        <f>P43*N43</f>
+        <v>0.99</v>
+      </c>
+      <c r="R43" s="14"/>
+    </row>
+    <row r="44" spans="1:18" s="47" customFormat="1">
+      <c r="A44" s="46"/>
+      <c r="B44" s="17">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="C44" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D44" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="E44" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="F44" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="G44" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="H44" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="I44" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="J44" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="K44" s="43" t="s">
+        <v>264</v>
+      </c>
+      <c r="L44" s="20">
+        <v>1</v>
+      </c>
+      <c r="M44" s="14">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N44" s="20">
+        <v>1100</v>
+      </c>
+      <c r="O44" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P44" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q44" s="21">
+        <f t="shared" ref="Q44" si="19">P44*N44</f>
+        <v>0.88</v>
+      </c>
+      <c r="R44" s="20"/>
+    </row>
+    <row r="45" spans="1:18" s="47" customFormat="1">
+      <c r="A45" s="46"/>
+      <c r="B45" s="16">
+        <f>ROW(B45) - ROW($B$7)</f>
+        <v>38</v>
+      </c>
+      <c r="C45" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="F45" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="G45" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="H45" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="I45" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="J45" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="K45" s="42" t="s">
+        <v>265</v>
+      </c>
+      <c r="L45" s="14">
+        <v>1</v>
+      </c>
+      <c r="M45" s="14">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N45" s="14">
+        <v>1020</v>
+      </c>
+      <c r="O45" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P45" s="15" t="s">
+        <v>365</v>
+      </c>
+      <c r="Q45" s="15">
+        <f>P45*N45</f>
+        <v>17.34</v>
+      </c>
+      <c r="R45" s="14"/>
+    </row>
+    <row r="46" spans="1:18" s="47" customFormat="1">
+      <c r="A46" s="46"/>
+      <c r="B46" s="17">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="C46" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D46" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="E46" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="F46" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="G46" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="H46" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="I46" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="J46" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="K46" s="43" t="s">
+        <v>266</v>
+      </c>
+      <c r="L46" s="20">
+        <v>1</v>
+      </c>
+      <c r="M46" s="14">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N46" s="20">
+        <v>1050</v>
+      </c>
+      <c r="O46" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P46" s="21" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q46" s="21">
+        <f t="shared" ref="Q46" si="20">P46*N46</f>
+        <v>15.75</v>
+      </c>
+      <c r="R46" s="20"/>
+    </row>
+    <row r="47" spans="1:18" s="47" customFormat="1">
+      <c r="A47" s="46"/>
+      <c r="B47" s="16">
+        <f>ROW(B47) - ROW($B$7)</f>
+        <v>40</v>
+      </c>
+      <c r="C47" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="E47" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="F47" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="G47" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="H47" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="I47" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="J47" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="K47" s="42" t="s">
+        <v>267</v>
+      </c>
+      <c r="L47" s="14">
+        <v>1</v>
+      </c>
+      <c r="M47" s="14">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N47" s="14">
+        <v>1020</v>
+      </c>
+      <c r="O47" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P47" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q47" s="15">
+        <f>P47*N47</f>
+        <v>17.135999999999999</v>
+      </c>
+      <c r="R47" s="14"/>
+    </row>
+    <row r="48" spans="1:18" s="47" customFormat="1" ht="24">
+      <c r="A48" s="46"/>
+      <c r="B48" s="17">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="C48" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D48" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="E48" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="F48" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="G48" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="H48" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="I48" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="J48" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="K48" s="43" t="s">
+        <v>268</v>
+      </c>
+      <c r="L48" s="20">
+        <v>12</v>
+      </c>
+      <c r="M48" s="14">
+        <f t="shared" si="1"/>
+        <v>12000</v>
+      </c>
+      <c r="N48" s="20">
+        <v>12005</v>
+      </c>
+      <c r="O48" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P48" s="21" t="s">
+        <v>367</v>
+      </c>
+      <c r="Q48" s="21">
+        <f t="shared" ref="Q48" si="21">P48*N48</f>
+        <v>1423.7929999999999</v>
+      </c>
+      <c r="R48" s="20"/>
+    </row>
+    <row r="49" spans="1:18" s="47" customFormat="1">
+      <c r="A49" s="46"/>
+      <c r="B49" s="16">
+        <f>ROW(B49) - ROW($B$7)</f>
+        <v>42</v>
+      </c>
+      <c r="C49" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D49" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E49" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="F49" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="G49" s="45" t="s">
+        <v>176</v>
+      </c>
+      <c r="H49" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="I49" s="14" t="s">
+        <v>328</v>
+      </c>
+      <c r="J49" s="14" t="s">
+        <v>327</v>
+      </c>
+      <c r="K49" s="42" t="s">
+        <v>264</v>
+      </c>
+      <c r="L49" s="14">
+        <v>6</v>
+      </c>
+      <c r="M49" s="14">
+        <f t="shared" si="1"/>
+        <v>6000</v>
+      </c>
+      <c r="N49" s="14">
+        <v>6050</v>
+      </c>
+      <c r="O49" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P49" s="15" t="s">
         <v>368</v>
       </c>
-      <c r="Q34" s="15">
-        <f>P34*N34</f>
-        <v>473.6454</v>
-      </c>
-      <c r="R34" s="14"/>
-    </row>
-    <row r="35" spans="1:18" s="50" customFormat="1" ht="25.5">
-      <c r="A35" s="49"/>
-      <c r="B35" s="17">
+      <c r="Q49" s="15">
+        <f>P49*N49</f>
+        <v>96.8</v>
+      </c>
+      <c r="R49" s="14"/>
+    </row>
+    <row r="50" spans="1:18" s="47" customFormat="1" ht="24">
+      <c r="A50" s="46"/>
+      <c r="B50" s="17">
         <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="C35" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="D35" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="E35" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="F35" s="20" t="s">
-        <v>290</v>
-      </c>
-      <c r="G35" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="H35" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="I35" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="J35" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="K35" s="46" t="s">
-        <v>263</v>
-      </c>
-      <c r="L35" s="20">
+        <v>43</v>
+      </c>
+      <c r="C50" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D50" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E50" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="F50" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="G50" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="H50" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="I50" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="J50" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="K50" s="43" t="s">
+        <v>280</v>
+      </c>
+      <c r="L50" s="20">
         <v>3</v>
       </c>
-      <c r="M35" s="14">
+      <c r="M50" s="14">
         <f t="shared" si="1"/>
         <v>3000</v>
       </c>
-      <c r="N35" s="20">
+      <c r="N50" s="20">
         <v>3010</v>
       </c>
-      <c r="O35" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P35" s="21" t="s">
+      <c r="O50" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="P50" s="21" t="s">
         <v>369</v>
       </c>
-      <c r="Q35" s="21">
-        <f t="shared" ref="Q35" si="15">P35*N35</f>
-        <v>119.497</v>
-      </c>
-      <c r="R35" s="20"/>
-    </row>
-    <row r="36" spans="1:18" s="50" customFormat="1">
-      <c r="A36" s="49"/>
-      <c r="B36" s="16">
-        <f>ROW(B36) - ROW($B$7)</f>
-        <v>29</v>
-      </c>
-      <c r="C36" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="D36" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="E36" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="F36" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="G36" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="H36" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="I36" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="J36" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="K36" s="45" t="s">
-        <v>264</v>
-      </c>
-      <c r="L36" s="14">
-        <v>6</v>
-      </c>
-      <c r="M36" s="14">
-        <f t="shared" si="1"/>
-        <v>6000</v>
-      </c>
-      <c r="N36" s="14">
-        <v>6050</v>
-      </c>
-      <c r="O36" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P36" s="15" t="s">
-        <v>370</v>
-      </c>
-      <c r="Q36" s="15">
-        <f>P36*N36</f>
-        <v>38.115000000000002</v>
-      </c>
-      <c r="R36" s="14"/>
-    </row>
-    <row r="37" spans="1:18" s="50" customFormat="1">
-      <c r="A37" s="49"/>
-      <c r="B37" s="17">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="C37" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="D37" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="E37" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="F37" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="G37" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="H37" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="I37" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="J37" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="K37" s="46" t="s">
-        <v>265</v>
-      </c>
-      <c r="L37" s="20">
-        <v>4</v>
-      </c>
-      <c r="M37" s="14">
-        <f t="shared" si="1"/>
-        <v>4000</v>
-      </c>
-      <c r="N37" s="20">
-        <v>4010</v>
-      </c>
-      <c r="O37" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P37" s="21" t="s">
-        <v>371</v>
-      </c>
-      <c r="Q37" s="21">
-        <f t="shared" ref="Q37" si="16">P37*N37</f>
-        <v>120.70099999999999</v>
-      </c>
-      <c r="R37" s="20"/>
-    </row>
-    <row r="38" spans="1:18" s="50" customFormat="1">
-      <c r="A38" s="49"/>
-      <c r="B38" s="16">
-        <f>ROW(B38) - ROW($B$7)</f>
-        <v>31</v>
-      </c>
-      <c r="C38" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="D38" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="E38" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="F38" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="G38" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="H38" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="I38" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="J38" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="K38" s="45" t="s">
-        <v>266</v>
-      </c>
-      <c r="L38" s="14">
-        <v>1</v>
-      </c>
-      <c r="M38" s="14">
-        <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="N38" s="14">
-        <v>1020</v>
-      </c>
-      <c r="O38" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P38" s="15" t="s">
-        <v>372</v>
-      </c>
-      <c r="Q38" s="15">
-        <f>P38*N38</f>
-        <v>19.686</v>
-      </c>
-      <c r="R38" s="14"/>
-    </row>
-    <row r="39" spans="1:18" s="50" customFormat="1">
-      <c r="A39" s="49"/>
-      <c r="B39" s="17">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="C39" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="D39" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="E39" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="F39" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="G39" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="H39" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="I39" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="J39" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="K39" s="46" t="s">
-        <v>267</v>
-      </c>
-      <c r="L39" s="20">
-        <v>1</v>
-      </c>
-      <c r="M39" s="14">
-        <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="N39" s="20">
-        <v>1010</v>
-      </c>
-      <c r="O39" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P39" s="21" t="s">
-        <v>373</v>
-      </c>
-      <c r="Q39" s="21">
-        <f t="shared" ref="Q39" si="17">P39*N39</f>
-        <v>32.723999999999997</v>
-      </c>
-      <c r="R39" s="20"/>
-    </row>
-    <row r="40" spans="1:18" s="50" customFormat="1">
-      <c r="A40" s="49"/>
-      <c r="B40" s="16">
-        <f>ROW(B40) - ROW($B$7)</f>
-        <v>33</v>
-      </c>
-      <c r="C40" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="E40" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="F40" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="G40" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="H40" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="I40" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="J40" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="K40" s="45" t="s">
-        <v>268</v>
-      </c>
-      <c r="L40" s="14">
-        <v>1</v>
-      </c>
-      <c r="M40" s="14">
-        <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="N40" s="14">
-        <v>1050</v>
-      </c>
-      <c r="O40" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P40" s="15" t="s">
-        <v>374</v>
-      </c>
-      <c r="Q40" s="15">
-        <f>P40*N40</f>
-        <v>9.0299999999999994</v>
-      </c>
-      <c r="R40" s="14"/>
-    </row>
-    <row r="41" spans="1:18" s="50" customFormat="1">
-      <c r="A41" s="49"/>
-      <c r="B41" s="17">
-        <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
-      <c r="C41" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="D41" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="E41" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="F41" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="G41" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="H41" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="I41" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="J41" s="20" t="s">
-        <v>236</v>
-      </c>
-      <c r="K41" s="46" t="s">
-        <v>269</v>
-      </c>
-      <c r="L41" s="20">
-        <v>1</v>
-      </c>
-      <c r="M41" s="14">
-        <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="N41" s="20">
-        <v>1100</v>
-      </c>
-      <c r="O41" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P41" s="21" t="s">
-        <v>375</v>
-      </c>
-      <c r="Q41" s="21">
-        <f t="shared" ref="Q41" si="18">P41*N41</f>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="R41" s="20"/>
-    </row>
-    <row r="42" spans="1:18" s="50" customFormat="1">
-      <c r="A42" s="49"/>
-      <c r="B42" s="16">
-        <f>ROW(B42) - ROW($B$7)</f>
-        <v>35</v>
-      </c>
-      <c r="C42" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D42" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="E42" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="F42" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="G42" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="H42" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="I42" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="J42" s="14" t="s">
-        <v>237</v>
-      </c>
-      <c r="K42" s="45" t="s">
-        <v>270</v>
-      </c>
-      <c r="L42" s="14">
-        <v>1</v>
-      </c>
-      <c r="M42" s="14">
-        <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="N42" s="14">
-        <v>1100</v>
-      </c>
-      <c r="O42" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P42" s="15" t="s">
-        <v>352</v>
-      </c>
-      <c r="Q42" s="15">
-        <f>P42*N42</f>
-        <v>1.8699999999999999</v>
-      </c>
-      <c r="R42" s="14"/>
-    </row>
-    <row r="43" spans="1:18" s="50" customFormat="1">
-      <c r="A43" s="49"/>
-      <c r="B43" s="17">
-        <f t="shared" si="0"/>
-        <v>36</v>
-      </c>
-      <c r="C43" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="D43" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="E43" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="F43" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="G43" s="20" t="s">
-        <v>174</v>
-      </c>
-      <c r="H43" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="I43" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="J43" s="20" t="s">
-        <v>238</v>
-      </c>
-      <c r="K43" s="46" t="s">
-        <v>271</v>
-      </c>
-      <c r="L43" s="20">
-        <v>1</v>
-      </c>
-      <c r="M43" s="14">
-        <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="N43" s="20">
-        <v>1100</v>
-      </c>
-      <c r="O43" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P43" s="21" t="s">
-        <v>376</v>
-      </c>
-      <c r="Q43" s="21">
-        <f t="shared" ref="Q43" si="19">P43*N43</f>
-        <v>0.65999999999999992</v>
-      </c>
-      <c r="R43" s="20"/>
-    </row>
-    <row r="44" spans="1:18" s="50" customFormat="1">
-      <c r="A44" s="49"/>
-      <c r="B44" s="16">
-        <f>ROW(B44) - ROW($B$7)</f>
-        <v>37</v>
-      </c>
-      <c r="C44" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="D44" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="E44" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="F44" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="G44" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="H44" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="I44" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="J44" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="K44" s="45" t="s">
-        <v>272</v>
-      </c>
-      <c r="L44" s="14">
-        <v>1</v>
-      </c>
-      <c r="M44" s="14">
-        <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="N44" s="14">
-        <v>1100</v>
-      </c>
-      <c r="O44" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P44" s="15" t="s">
-        <v>377</v>
-      </c>
-      <c r="Q44" s="15">
-        <f>P44*N44</f>
-        <v>0.99</v>
-      </c>
-      <c r="R44" s="14"/>
-    </row>
-    <row r="45" spans="1:18" s="50" customFormat="1">
-      <c r="A45" s="49"/>
-      <c r="B45" s="17">
-        <f t="shared" si="0"/>
-        <v>38</v>
-      </c>
-      <c r="C45" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="D45" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="E45" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="F45" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="G45" s="20" t="s">
-        <v>176</v>
-      </c>
-      <c r="H45" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="I45" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="J45" s="20" t="s">
-        <v>240</v>
-      </c>
-      <c r="K45" s="46" t="s">
-        <v>273</v>
-      </c>
-      <c r="L45" s="20">
-        <v>1</v>
-      </c>
-      <c r="M45" s="14">
-        <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="N45" s="20">
-        <v>1100</v>
-      </c>
-      <c r="O45" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P45" s="21" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q45" s="21">
-        <f t="shared" ref="Q45" si="20">P45*N45</f>
-        <v>0.88</v>
-      </c>
-      <c r="R45" s="20"/>
-    </row>
-    <row r="46" spans="1:18" s="50" customFormat="1">
-      <c r="A46" s="49"/>
-      <c r="B46" s="16">
-        <f>ROW(B46) - ROW($B$7)</f>
-        <v>39</v>
-      </c>
-      <c r="C46" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="D46" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="E46" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="F46" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="G46" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="H46" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="I46" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="J46" s="14" t="s">
-        <v>241</v>
-      </c>
-      <c r="K46" s="45" t="s">
-        <v>274</v>
-      </c>
-      <c r="L46" s="14">
-        <v>1</v>
-      </c>
-      <c r="M46" s="14">
-        <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="N46" s="14">
-        <v>1020</v>
-      </c>
-      <c r="O46" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P46" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="Q46" s="15">
-        <f>P46*N46</f>
-        <v>17.34</v>
-      </c>
-      <c r="R46" s="14"/>
-    </row>
-    <row r="47" spans="1:18" s="50" customFormat="1">
-      <c r="A47" s="49"/>
-      <c r="B47" s="17">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="C47" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="D47" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="E47" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="F47" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="G47" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="H47" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="I47" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="J47" s="20" t="s">
-        <v>242</v>
-      </c>
-      <c r="K47" s="46" t="s">
-        <v>275</v>
-      </c>
-      <c r="L47" s="20">
-        <v>1</v>
-      </c>
-      <c r="M47" s="14">
-        <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="N47" s="20">
-        <v>1050</v>
-      </c>
-      <c r="O47" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P47" s="21" t="s">
-        <v>379</v>
-      </c>
-      <c r="Q47" s="21">
-        <f t="shared" ref="Q47" si="21">P47*N47</f>
-        <v>15.75</v>
-      </c>
-      <c r="R47" s="20"/>
-    </row>
-    <row r="48" spans="1:18" s="50" customFormat="1">
-      <c r="A48" s="49"/>
-      <c r="B48" s="16">
-        <f>ROW(B48) - ROW($B$7)</f>
-        <v>41</v>
-      </c>
-      <c r="C48" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="D48" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E48" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="F48" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="G48" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="H48" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="I48" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="J48" s="14" t="s">
-        <v>243</v>
-      </c>
-      <c r="K48" s="45" t="s">
-        <v>276</v>
-      </c>
-      <c r="L48" s="14">
-        <v>1</v>
-      </c>
-      <c r="M48" s="14">
-        <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="N48" s="14">
-        <v>1020</v>
-      </c>
-      <c r="O48" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P48" s="15" t="s">
-        <v>357</v>
-      </c>
-      <c r="Q48" s="15">
-        <f>P48*N48</f>
-        <v>17.135999999999999</v>
-      </c>
-      <c r="R48" s="14"/>
-    </row>
-    <row r="49" spans="1:18" s="50" customFormat="1" ht="24">
-      <c r="A49" s="49"/>
-      <c r="B49" s="17">
-        <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
-      <c r="C49" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="D49" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="E49" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="F49" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="G49" s="20" t="s">
-        <v>180</v>
-      </c>
-      <c r="H49" s="20" t="s">
-        <v>202</v>
-      </c>
-      <c r="I49" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="J49" s="20" t="s">
-        <v>244</v>
-      </c>
-      <c r="K49" s="46" t="s">
-        <v>277</v>
-      </c>
-      <c r="L49" s="20">
-        <v>12</v>
-      </c>
-      <c r="M49" s="14">
-        <f t="shared" si="1"/>
-        <v>12000</v>
-      </c>
-      <c r="N49" s="20">
-        <v>12005</v>
-      </c>
-      <c r="O49" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P49" s="21" t="s">
-        <v>380</v>
-      </c>
-      <c r="Q49" s="21">
-        <f t="shared" ref="Q49" si="22">P49*N49</f>
-        <v>1423.7929999999999</v>
-      </c>
-      <c r="R49" s="20"/>
-    </row>
-    <row r="50" spans="1:18" s="50" customFormat="1">
-      <c r="A50" s="49"/>
-      <c r="B50" s="16">
-        <f>ROW(B50) - ROW($B$7)</f>
-        <v>43</v>
-      </c>
-      <c r="C50" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D50" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="E50" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="F50" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="G50" s="48" t="s">
-        <v>181</v>
-      </c>
-      <c r="H50" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="I50" s="14" t="s">
-        <v>339</v>
-      </c>
-      <c r="J50" s="14" t="s">
-        <v>338</v>
-      </c>
-      <c r="K50" s="45" t="s">
-        <v>273</v>
-      </c>
-      <c r="L50" s="14">
-        <v>6</v>
-      </c>
-      <c r="M50" s="14">
-        <f t="shared" si="1"/>
-        <v>6000</v>
-      </c>
-      <c r="N50" s="14">
-        <v>6050</v>
-      </c>
-      <c r="O50" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P50" s="15" t="s">
-        <v>381</v>
-      </c>
-      <c r="Q50" s="15">
-        <f>P50*N50</f>
-        <v>96.8</v>
-      </c>
-      <c r="R50" s="14"/>
-    </row>
-    <row r="51" spans="1:18" s="50" customFormat="1" ht="24">
-      <c r="A51" s="49"/>
+      <c r="Q50" s="21">
+        <f t="shared" ref="Q50:Q51" si="22">P50*N50</f>
+        <v>128.226</v>
+      </c>
+      <c r="R50" s="20"/>
+    </row>
+    <row r="51" spans="1:18">
+      <c r="A51" s="1"/>
       <c r="B51" s="17">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="C51" s="23" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D51" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="E51" s="20" t="s">
-        <v>116</v>
+        <v>372</v>
+      </c>
+      <c r="E51" s="43" t="s">
+        <v>373</v>
       </c>
       <c r="F51" s="20" t="s">
-        <v>290</v>
-      </c>
-      <c r="G51" s="20" t="s">
-        <v>144</v>
+        <v>281</v>
+      </c>
+      <c r="G51" s="43" t="s">
+        <v>374</v>
       </c>
       <c r="H51" s="20" t="s">
-        <v>194</v>
+        <v>280</v>
       </c>
       <c r="I51" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="J51" s="20" t="s">
-        <v>245</v>
-      </c>
-      <c r="K51" s="46" t="s">
-        <v>289</v>
-      </c>
-      <c r="L51" s="20">
-        <v>3</v>
+        <v>280</v>
+      </c>
+      <c r="J51" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="K51" s="43"/>
+      <c r="L51" s="14">
+        <v>1</v>
       </c>
       <c r="M51" s="14">
         <f t="shared" si="1"/>
-        <v>3000</v>
-      </c>
-      <c r="N51" s="20">
-        <v>3010</v>
-      </c>
-      <c r="O51" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="P51" s="21" t="s">
-        <v>382</v>
+        <v>1000</v>
+      </c>
+      <c r="N51" s="14">
+        <v>1002</v>
+      </c>
+      <c r="O51" s="44" t="s">
+        <v>280</v>
+      </c>
+      <c r="P51" s="21">
+        <v>0.93</v>
       </c>
       <c r="Q51" s="21">
-        <f t="shared" ref="Q51" si="23">P51*N51</f>
-        <v>128.226</v>
-      </c>
-      <c r="R51" s="20"/>
-    </row>
-    <row r="52" spans="1:18" s="50" customFormat="1" ht="36">
-      <c r="A52" s="49"/>
+        <f t="shared" si="22"/>
+        <v>931.86</v>
+      </c>
+      <c r="R51" s="14"/>
+    </row>
+    <row r="52" spans="1:18" s="47" customFormat="1" ht="36">
+      <c r="A52" s="46"/>
       <c r="B52" s="16">
         <f>ROW(B52) - ROW($B$7)</f>
         <v>45</v>
@@ -7489,28 +7480,28 @@
         <v>24</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="G52" s="14" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="H52" s="14" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="I52" s="20" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J52" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="K52" s="46" t="s">
-        <v>289</v>
+        <v>237</v>
+      </c>
+      <c r="K52" s="43" t="s">
+        <v>280</v>
       </c>
       <c r="L52" s="14">
         <v>1</v>
@@ -7522,11 +7513,11 @@
       <c r="N52" s="14">
         <v>1002</v>
       </c>
-      <c r="O52" s="47" t="s">
-        <v>313</v>
+      <c r="O52" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P52" s="15" t="s">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="Q52" s="15">
         <f>P52*N52</f>
@@ -7534,8 +7525,8 @@
       </c>
       <c r="R52" s="14"/>
     </row>
-    <row r="53" spans="1:18" s="50" customFormat="1" ht="36">
-      <c r="A53" s="49"/>
+    <row r="53" spans="1:18" s="47" customFormat="1" ht="36">
+      <c r="A53" s="46"/>
       <c r="B53" s="17">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -7544,28 +7535,28 @@
         <v>24</v>
       </c>
       <c r="D53" s="20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F53" s="20" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="G53" s="20" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="H53" s="20" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I53" s="20" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J53" s="20" t="s">
-        <v>247</v>
-      </c>
-      <c r="K53" s="46" t="s">
-        <v>289</v>
+        <v>238</v>
+      </c>
+      <c r="K53" s="43" t="s">
+        <v>280</v>
       </c>
       <c r="L53" s="20">
         <v>1</v>
@@ -7577,20 +7568,20 @@
       <c r="N53" s="20">
         <v>1005</v>
       </c>
-      <c r="O53" s="47" t="s">
-        <v>313</v>
+      <c r="O53" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P53" s="21" t="s">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="Q53" s="21">
-        <f t="shared" ref="Q53" si="24">P53*N53</f>
+        <f t="shared" ref="Q53" si="23">P53*N53</f>
         <v>132.459</v>
       </c>
       <c r="R53" s="20"/>
     </row>
-    <row r="54" spans="1:18" s="50" customFormat="1" ht="24.75" thickBot="1">
-      <c r="A54" s="49"/>
+    <row r="54" spans="1:18" s="47" customFormat="1" ht="24.75" thickBot="1">
+      <c r="A54" s="46"/>
       <c r="B54" s="16">
         <f>ROW(B54) - ROW($B$7)</f>
         <v>47</v>
@@ -7599,28 +7590,28 @@
         <v>24</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G54" s="14" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="H54" s="14" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="I54" s="20" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J54" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="K54" s="46" t="s">
-        <v>289</v>
+        <v>239</v>
+      </c>
+      <c r="K54" s="43" t="s">
+        <v>280</v>
       </c>
       <c r="L54" s="14">
         <v>1</v>
@@ -7632,11 +7623,11 @@
       <c r="N54" s="14">
         <v>1005</v>
       </c>
-      <c r="O54" s="47" t="s">
-        <v>313</v>
+      <c r="O54" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="P54" s="15" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="Q54" s="15">
         <f>P54*N54</f>
@@ -7658,14 +7649,14 @@
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
       <c r="M55" s="1"/>
-      <c r="N55" s="43" t="s">
+      <c r="N55" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="O55" s="44"/>
-      <c r="P55" s="44"/>
+      <c r="O55" s="50"/>
+      <c r="P55" s="50"/>
       <c r="Q55" s="18">
         <f>SUM(Q8:Q54)</f>
-        <v>9451.0178000000014</v>
+        <v>9710.8852999999999</v>
       </c>
       <c r="R55" s="1"/>
     </row>
@@ -7683,14 +7674,14 @@
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
       <c r="M56" s="1"/>
-      <c r="N56" s="43" t="s">
+      <c r="N56" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="O56" s="44"/>
-      <c r="P56" s="44"/>
+      <c r="O56" s="50"/>
+      <c r="P56" s="50"/>
       <c r="Q56" s="19">
         <f>Q55/1000</f>
-        <v>9.4510178000000007</v>
+        <v>9.7108852999999993</v>
       </c>
       <c r="R56" s="1"/>
     </row>
@@ -7720,33 +7711,33 @@
     <hyperlink ref="O26" r:id="rId17"/>
     <hyperlink ref="O27" r:id="rId18"/>
     <hyperlink ref="O28" r:id="rId19"/>
-    <hyperlink ref="O30" r:id="rId20"/>
-    <hyperlink ref="O31" r:id="rId21"/>
-    <hyperlink ref="O32" r:id="rId22"/>
-    <hyperlink ref="O34" r:id="rId23"/>
-    <hyperlink ref="O35" r:id="rId24"/>
-    <hyperlink ref="O36" r:id="rId25"/>
-    <hyperlink ref="O37" r:id="rId26"/>
-    <hyperlink ref="O38" r:id="rId27"/>
-    <hyperlink ref="O39" r:id="rId28"/>
-    <hyperlink ref="O40" r:id="rId29"/>
-    <hyperlink ref="O41" r:id="rId30"/>
-    <hyperlink ref="O42" r:id="rId31"/>
-    <hyperlink ref="O43" r:id="rId32"/>
-    <hyperlink ref="O44" r:id="rId33"/>
-    <hyperlink ref="O45" r:id="rId34"/>
-    <hyperlink ref="O46" r:id="rId35"/>
-    <hyperlink ref="O47" r:id="rId36"/>
-    <hyperlink ref="O48" r:id="rId37"/>
-    <hyperlink ref="O49" r:id="rId38"/>
-    <hyperlink ref="O51" r:id="rId39"/>
-    <hyperlink ref="O52" r:id="rId40"/>
-    <hyperlink ref="O53" r:id="rId41"/>
-    <hyperlink ref="O54" r:id="rId42"/>
-    <hyperlink ref="O9" r:id="rId43"/>
-    <hyperlink ref="O21" r:id="rId44"/>
-    <hyperlink ref="O29" r:id="rId45"/>
-    <hyperlink ref="O50" r:id="rId46"/>
+    <hyperlink ref="O32" r:id="rId20"/>
+    <hyperlink ref="O33" r:id="rId21"/>
+    <hyperlink ref="O34" r:id="rId22"/>
+    <hyperlink ref="O35" r:id="rId23"/>
+    <hyperlink ref="O36" r:id="rId24"/>
+    <hyperlink ref="O37" r:id="rId25"/>
+    <hyperlink ref="O38" r:id="rId26"/>
+    <hyperlink ref="O39" r:id="rId27"/>
+    <hyperlink ref="O40" r:id="rId28"/>
+    <hyperlink ref="O41" r:id="rId29"/>
+    <hyperlink ref="O42" r:id="rId30"/>
+    <hyperlink ref="O43" r:id="rId31"/>
+    <hyperlink ref="O44" r:id="rId32"/>
+    <hyperlink ref="O45" r:id="rId33"/>
+    <hyperlink ref="O46" r:id="rId34"/>
+    <hyperlink ref="O47" r:id="rId35"/>
+    <hyperlink ref="O48" r:id="rId36"/>
+    <hyperlink ref="O50" r:id="rId37"/>
+    <hyperlink ref="O52" r:id="rId38"/>
+    <hyperlink ref="O53" r:id="rId39"/>
+    <hyperlink ref="O54" r:id="rId40"/>
+    <hyperlink ref="O9" r:id="rId41"/>
+    <hyperlink ref="O21" r:id="rId42"/>
+    <hyperlink ref="O29" r:id="rId43"/>
+    <hyperlink ref="O49" r:id="rId44"/>
+    <hyperlink ref="O31" r:id="rId45"/>
+    <hyperlink ref="O30" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Design-Files/OFP_VIM_v1.5/BOM/eSpark-BOM-OFP_VIM_v1.5.xlsx
+++ b/Design-Files/OFP_VIM_v1.5/BOM/eSpark-BOM-OFP_VIM_v1.5.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="10 Boards" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="382">
   <si>
     <t>Component list</t>
   </si>
@@ -4561,12 +4561,11 @@
       <c r="O51" s="44" t="s">
         <v>280</v>
       </c>
-      <c r="P51" s="21">
-        <v>3</v>
-      </c>
-      <c r="Q51" s="21">
-        <f t="shared" si="22"/>
-        <v>33</v>
+      <c r="P51" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q51" s="21" t="s">
+        <v>280</v>
       </c>
       <c r="R51" s="14"/>
     </row>
@@ -4756,7 +4755,7 @@
       <c r="P55" s="50"/>
       <c r="Q55" s="18">
         <f>SUM(Q8:Q54)</f>
-        <v>196.70939999999999</v>
+        <v>163.70939999999999</v>
       </c>
       <c r="R55" s="1"/>
     </row>
@@ -4781,7 +4780,7 @@
       <c r="P56" s="50"/>
       <c r="Q56" s="19">
         <f>Q55/10</f>
-        <v>19.670939999999998</v>
+        <v>16.370939999999997</v>
       </c>
       <c r="R56" s="1"/>
     </row>
@@ -7461,12 +7460,11 @@
       <c r="O51" s="44" t="s">
         <v>280</v>
       </c>
-      <c r="P51" s="21">
-        <v>0.93</v>
-      </c>
-      <c r="Q51" s="21">
-        <f t="shared" si="22"/>
-        <v>931.86</v>
+      <c r="P51" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q51" s="21" t="s">
+        <v>280</v>
       </c>
       <c r="R51" s="14"/>
     </row>
@@ -7656,7 +7654,7 @@
       <c r="P55" s="50"/>
       <c r="Q55" s="18">
         <f>SUM(Q8:Q54)</f>
-        <v>9710.8852999999999</v>
+        <v>8779.0253000000012</v>
       </c>
       <c r="R55" s="1"/>
     </row>
@@ -7681,7 +7679,7 @@
       <c r="P56" s="50"/>
       <c r="Q56" s="19">
         <f>Q55/1000</f>
-        <v>9.7108852999999993</v>
+        <v>8.7790253000000007</v>
       </c>
       <c r="R56" s="1"/>
     </row>
